--- a/Alice_Fleet_ROI_Optimizer.xlsx
+++ b/Alice_Fleet_ROI_Optimizer.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xinxuangan_home/Downloads/Projects-DA.ipynb/Project_Alice_Aviation.ipynb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DA8B5D-6C6E-2D48-86CC-1F3C1290A970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8282D724-361F-CD45-8123-529C28A8EB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="780" windowWidth="34200" windowHeight="20060" xr2:uid="{545C68F0-ED14-434A-8B04-9F97BEFF5D98}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="20020" xr2:uid="{545C68F0-ED14-434A-8B04-9F97BEFF5D98}"/>
   </bookViews>
   <sheets>
     <sheet name="Executive Summary" sheetId="3" r:id="rId1"/>
@@ -66,7 +66,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="89" r:id="rId7"/>
+    <pivotCache cacheId="90" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="231">
   <si>
     <t>flight_id</t>
   </si>
@@ -669,9 +669,6 @@
   </si>
   <si>
     <t>Payload</t>
-  </si>
-  <si>
-    <t>In the previous project, the initial Python Stress Test proved that a 75-minute mission profile leads to a 100% safety breach. This Excel model investigates the Commercial Viability of the 60-minute "Safe Zone" to determine if Eviation Alice can remain profitable and HOW while staying 100% FAA-compliant.</t>
   </si>
   <si>
     <t>Insights</t>
@@ -943,6 +940,12 @@
   <si>
     <t>% SoC</t>
   </si>
+  <si>
+    <t>This strategic model evaluates the commercial viability of the Eviation Alice (all-electric aircraft) by bridging the gap between high-frequency physics telemetry and fleet unit economics. Utilizing an end-to-end analytical pipeline, the system integrates a 96%-accuracy predictive ML model into an interactive financial optimizer, enabling real-time ROI simulations across 100 regional mission scenarios.</t>
+  </si>
+  <si>
+    <t>Objective: To maximize fleet EBITDA through constrained optimization, identifying the optimal balance between cargo density, ambient thermal stress, and a regional grid energy ceiling while enforcing compliance with FAA safety mandates.</t>
+  </si>
 </sst>
 </file>
 
@@ -952,10 +955,10 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="0.0000"/>
-    <numFmt numFmtId="183" formatCode="0.0000000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0000000000"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1201,27 +1204,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Aptos Narrow"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <i/>
       <sz val="12"/>
       <color rgb="FF7F7F7F"/>
@@ -1245,6 +1227,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="16"/>
       <color rgb="FFFA7D00"/>
       <name val="Aptos Narrow"/>
@@ -1432,7 +1441,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1739,6 +1748,33 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color theme="4"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1786,7 +1822,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1813,12 +1849,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="12"/>
-    <xf numFmtId="9" fontId="10" fillId="6" borderId="5" xfId="12" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="12" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1854,14 +1884,6 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="30" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" xfId="17" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="6" borderId="5" xfId="12" applyFont="1"/>
-    <xf numFmtId="9" fontId="10" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="44" fontId="9" fillId="5" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1890,49 +1912,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="10" fillId="6" borderId="5" xfId="12" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="6" xfId="14" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="8" xfId="17" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="16" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="10" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="10" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1951,35 +1931,105 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="21" xfId="13" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="183" fontId="40" fillId="6" borderId="21" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="21" xfId="13" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="37" fillId="6" borderId="21" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="176" fontId="40" fillId="6" borderId="21" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="37" fillId="6" borderId="21" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="21" xfId="12" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="39" fillId="6" borderId="21" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="21" xfId="12" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="36" fillId="6" borderId="21" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="21" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="21" xfId="12" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="6" borderId="24" xfId="13" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="6" borderId="24" xfId="13" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="29" fillId="5" borderId="24" xfId="11" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="39" fillId="6" borderId="24" xfId="12" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="39" fillId="6" borderId="21" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="6" borderId="24" xfId="12" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="36" fillId="6" borderId="21" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="39" fillId="6" borderId="21" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="36" fillId="6" borderId="21" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="4" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="8" borderId="8" xfId="17" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="16" xfId="18" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="26" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="27" xfId="18" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="18" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="5" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="5" xfId="12" applyFont="1"/>
+    <xf numFmtId="44" fontId="39" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="40" fillId="6" borderId="5" xfId="12" applyFont="1"/>
+    <xf numFmtId="9" fontId="39" fillId="6" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="9" fontId="39" fillId="6" borderId="5" xfId="12" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="5" xfId="12" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="39" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="6" xfId="14" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="5" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="2" xfId="5" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="44">
@@ -2030,6 +2080,9 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
+      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
@@ -2065,9 +2118,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3876,7 +3926,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7914F8C7-A6CA-8746-A850-FFDFF9A54023}" name="PivotTable20" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7914F8C7-A6CA-8746-A850-FFDFF9A54023}" name="PivotTable20" cacheId="90" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A1:C22" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -4016,7 +4066,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB2A47E2-52F4-1F4A-A30D-AA00B807654F}" name="PivotTable21" cacheId="89" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AB2A47E2-52F4-1F4A-A30D-AA00B807654F}" name="PivotTable21" cacheId="90" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A1:E4" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="14">
     <pivotField showAll="0"/>
@@ -4116,12 +4166,12 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C22FCAD9-EF85-D342-A324-E525567EDF73}" name="Alice_Master_Analysis" displayName="Alice_Master_Analysis" ref="A1:N101" tableType="queryTable" totalsRowShown="0">
   <autoFilter ref="A1:N101" xr:uid="{C22FCAD9-EF85-D342-A324-E525567EDF73}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{65DD2AD6-6CFD-1747-A28B-BE7B48377530}" uniqueName="1" name="flight_id" queryTableFieldId="1" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{65DD2AD6-6CFD-1747-A28B-BE7B48377530}" uniqueName="1" name="flight_id" queryTableFieldId="1" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{D85AD181-1BA5-3446-9353-E0AA1C70C694}" uniqueName="2" name="Safe_Duration_Min" queryTableFieldId="2"/>
     <tableColumn id="3" xr3:uid="{457FB175-56D8-BD48-8AE9-AEE2F70874EF}" uniqueName="3" name="Start_SoC" queryTableFieldId="3"/>
     <tableColumn id="4" xr3:uid="{37A2473D-CD4E-834A-AAE0-95746A0C9982}" uniqueName="4" name="End_SoC" queryTableFieldId="4"/>
     <tableColumn id="5" xr3:uid="{AEC598A2-BA97-F445-BA45-7DC2666B5967}" uniqueName="5" name="Payload" queryTableFieldId="5"/>
-    <tableColumn id="6" xr3:uid="{D7CFDD01-F309-654D-9F79-D08D5E479C94}" uniqueName="6" name="Firmware" queryTableFieldId="6" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{D7CFDD01-F309-654D-9F79-D08D5E479C94}" uniqueName="6" name="Firmware" queryTableFieldId="6" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{932A4D6B-5EF4-6847-B50D-150FA83A16DE}" uniqueName="7" name="Temp" queryTableFieldId="7"/>
     <tableColumn id="8" xr3:uid="{5F00E08C-D831-BC4B-846D-DFA76B7B5109}" uniqueName="8" name="Net_kWh_used" queryTableFieldId="8"/>
     <tableColumn id="9" xr3:uid="{6E01F57A-E86F-7940-B52D-A50504740E65}" uniqueName="9" name="Sortie Revenue" queryTableFieldId="9" dataCellStyle="Currency">
@@ -4133,10 +4183,10 @@
     <tableColumn id="11" xr3:uid="{B8AFA812-0F82-1E42-AC8B-640903E41113}" uniqueName="11" name="Battery Depreciation" queryTableFieldId="11" dataCellStyle="Currency">
       <calculatedColumnFormula>(Alice_Master_Analysis[[#This Row],[Net_kWh_used]]/850)*(val_battery_cost/val_cycle)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{A175C20C-7176-DB41-BFF4-DBB112FC0775}" uniqueName="12" name="Total OpEx per Sortie" queryTableFieldId="12" dataDxfId="4" dataCellStyle="Currency">
+    <tableColumn id="12" xr3:uid="{A175C20C-7176-DB41-BFF4-DBB112FC0775}" uniqueName="12" name="Total OpEx per Sortie" queryTableFieldId="12" dataDxfId="5" dataCellStyle="Currency">
       <calculatedColumnFormula>Alice_Master_Analysis[[#This Row],[Energy Cost]]+Alice_Master_Analysis[[#This Row],[Battery Depreciation]]+val_ground_ops</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{124B15FE-FE0F-7B46-912D-62F90F078279}" uniqueName="13" name="Net Profit" queryTableFieldId="13" dataDxfId="3" dataCellStyle="Currency">
+    <tableColumn id="13" xr3:uid="{124B15FE-FE0F-7B46-912D-62F90F078279}" uniqueName="13" name="Net Profit" queryTableFieldId="13" dataDxfId="4" dataCellStyle="Currency">
       <calculatedColumnFormula>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="14" xr3:uid="{BCDAE1FF-7CFA-1A4D-BDC7-E34050A0553F}" uniqueName="14" name="EBIDTA(%)" queryTableFieldId="14" dataCellStyle="Percent">
@@ -4151,17 +4201,17 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{52001225-107B-344E-855F-A178662FAA5A}" name="Table7" displayName="Table7" ref="A1:F101" totalsRowShown="0">
   <autoFilter ref="A1:F101" xr:uid="{52001225-107B-344E-855F-A178662FAA5A}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{95B23015-0F2C-B949-BF62-F3C4B7804ACB}" name="flight_id" dataDxfId="2">
+    <tableColumn id="1" xr3:uid="{95B23015-0F2C-B949-BF62-F3C4B7804ACB}" name="flight_id" dataDxfId="3">
       <calculatedColumnFormula>Alice_Master_Analysis[[#This Row],[flight_id]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{803CA7D3-512F-B347-B805-C95D6435B7B8}" name="Net_Profit" dataDxfId="1" dataCellStyle="Currency">
+    <tableColumn id="2" xr3:uid="{803CA7D3-512F-B347-B805-C95D6435B7B8}" name="Net_Profit" dataDxfId="2" dataCellStyle="Currency">
       <calculatedColumnFormula>Alice_Master_Analysis[[#This Row],[Net Profit]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{F81FF4CA-02CC-F14A-8D56-EA1EAEBBEAF4}" name="Energy_kWh" dataDxfId="0">
+    <tableColumn id="3" xr3:uid="{F81FF4CA-02CC-F14A-8D56-EA1EAEBBEAF4}" name="Energy_kWh" dataDxfId="1">
       <calculatedColumnFormula>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="4" xr3:uid="{258F74F6-39CB-604A-A19A-2942501897E2}" name="Flight Decision"/>
-    <tableColumn id="5" xr3:uid="{FEBE3E5F-2876-F944-A459-78AF77EC23CB}" name="Opt.Profit" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{FEBE3E5F-2876-F944-A459-78AF77EC23CB}" name="Opt.Profit" dataDxfId="0">
       <calculatedColumnFormula>B2*D2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="6" xr3:uid="{37BE7D2A-0171-744C-9658-9293A3F687CA}" name="Opt.Energy">
@@ -4493,8 +4543,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="24.6640625" customWidth="1"/>
-    <col min="2" max="2" width="9.83203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="19.5" customWidth="1"/>
+    <col min="2" max="2" width="15" style="5" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="4" width="36.6640625" customWidth="1"/>
     <col min="6" max="6" width="21.6640625" customWidth="1"/>
     <col min="7" max="7" width="12.5" bestFit="1" customWidth="1"/>
@@ -4502,97 +4552,104 @@
     <col min="9" max="9" width="47.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" ht="21" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+    <row r="2" spans="1:15" ht="23" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="78" t="s">
         <v>188</v>
       </c>
-      <c r="B2" s="64"/>
-      <c r="C2" s="64"/>
-      <c r="D2" s="64"/>
+      <c r="B2" s="78"/>
+      <c r="C2" s="78"/>
+      <c r="D2" s="78"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="63" t="s">
+      <c r="F2" s="105" t="s">
         <v>189</v>
       </c>
-      <c r="G2" s="63"/>
-      <c r="H2" s="63"/>
-      <c r="I2" s="63"/>
+      <c r="G2" s="105"/>
+      <c r="H2" s="105"/>
+      <c r="I2" s="105"/>
     </row>
     <row r="3" spans="1:15" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="89" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="89"/>
+      <c r="C3" s="89"/>
+      <c r="D3" s="89"/>
       <c r="E3" s="2"/>
-      <c r="F3" s="43" t="s">
+      <c r="F3" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="44">
+      <c r="G3" s="11">
         <v>850</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="I3" s="42" t="s">
+      <c r="I3" s="40" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A4" s="65" t="s">
-        <v>191</v>
-      </c>
-      <c r="B4" s="65"/>
-      <c r="C4" s="65"/>
-      <c r="D4" s="65"/>
+      <c r="A4" s="90"/>
+      <c r="B4" s="90"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="90"/>
       <c r="E4" s="2"/>
-      <c r="F4" s="43" t="s">
+      <c r="F4" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="G4" s="44">
+      <c r="G4" s="11">
         <v>2500</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="I4" s="42" t="s">
+      <c r="I4" s="40" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A5" s="65"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
+      <c r="A5" s="90"/>
+      <c r="B5" s="90"/>
+      <c r="C5" s="90"/>
+      <c r="D5" s="90"/>
       <c r="E5" s="2"/>
       <c r="F5" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="G5" s="47">
+      <c r="G5" s="11">
         <v>0.18</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="40" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A6" s="65"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="65"/>
-      <c r="D6" s="65"/>
+      <c r="A6" s="90"/>
+      <c r="B6" s="90"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="90"/>
       <c r="E6" s="2"/>
       <c r="F6" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="G6" s="48">
+      <c r="G6" s="42">
         <v>350000</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="I6" s="42" t="s">
+      <c r="I6" s="40" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B7"/>
+      <c r="A7" s="88"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
       <c r="E7" s="2"/>
       <c r="F7" s="11" t="s">
         <v>114</v>
@@ -4603,258 +4660,276 @@
       <c r="H7" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="I7" s="42" t="s">
+      <c r="I7" s="40" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
-      <c r="B8" s="13"/>
-      <c r="C8" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="D8" s="13">
-        <v>100</v>
-      </c>
+      <c r="A8" s="93" t="s">
+        <v>230</v>
+      </c>
+      <c r="B8" s="93"/>
+      <c r="C8" s="93"/>
+      <c r="D8" s="93"/>
       <c r="E8" s="2"/>
       <c r="F8" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="G8" s="47">
+      <c r="G8" s="41">
         <v>0.25</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="40" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="12" t="s">
-        <v>218</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>219</v>
-      </c>
+      <c r="A9" s="94"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="94"/>
+      <c r="D9" s="94"/>
       <c r="E9" s="2"/>
       <c r="F9" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="G9" s="48">
+      <c r="G9" s="42">
         <v>1200</v>
       </c>
       <c r="H9" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="I9" s="42" t="s">
+      <c r="I9" s="40" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="94"/>
+      <c r="B10" s="94"/>
+      <c r="C10" s="94"/>
+      <c r="D10" s="94"/>
       <c r="F10" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="G10" s="49">
+      <c r="G10" s="43">
         <v>1.1200000000000001</v>
       </c>
       <c r="H10" s="11"/>
-      <c r="I10" s="42"/>
+      <c r="I10" s="40"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="92"/>
+      <c r="B11" s="92"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="92"/>
       <c r="E11" s="2"/>
       <c r="F11" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="G11" s="47">
+      <c r="G11" s="41">
         <v>2.25</v>
       </c>
       <c r="H11" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="I11" s="42" t="s">
+      <c r="I11" s="40" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="19" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F13" s="63" t="s">
-        <v>193</v>
-      </c>
-      <c r="G13" s="63"/>
-      <c r="H13" s="63"/>
-      <c r="I13" s="63"/>
-      <c r="J13" s="63"/>
-      <c r="K13" s="63"/>
-      <c r="L13" s="63"/>
-      <c r="M13" s="63"/>
-      <c r="N13" s="63"/>
-      <c r="O13" s="63"/>
-    </row>
-    <row r="14" spans="1:15" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="60" t="s">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="91"/>
+      <c r="B12" s="91"/>
+      <c r="C12" s="91"/>
+      <c r="D12" s="91"/>
+    </row>
+    <row r="14" spans="1:15" ht="23" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="103" t="s">
+        <v>191</v>
+      </c>
+      <c r="B14" s="103"/>
+      <c r="C14" s="103"/>
+      <c r="D14" s="103"/>
+      <c r="F14" s="104" t="s">
         <v>192</v>
       </c>
-      <c r="B14" s="60"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="60"/>
-      <c r="F14" s="15" t="s">
+      <c r="G14" s="104"/>
+      <c r="H14" s="104"/>
+      <c r="I14" s="104"/>
+      <c r="J14" s="95"/>
+      <c r="K14" s="95"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
+      <c r="N14" s="95"/>
+      <c r="O14" s="95"/>
+    </row>
+    <row r="15" spans="1:15" ht="16" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="76" t="s">
+        <v>213</v>
+      </c>
+      <c r="B15" s="77"/>
+      <c r="C15" s="77"/>
+      <c r="D15" s="77"/>
+      <c r="F15" s="96" t="s">
         <v>174</v>
       </c>
-      <c r="G14" s="76">
+      <c r="G15" s="97">
         <f>SUM(Alice_ROI_Analysis!M:M)</f>
         <v>173786.85551686084</v>
       </c>
-      <c r="H14" s="45"/>
-    </row>
-    <row r="15" spans="1:15" ht="16" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="59" t="s">
-        <v>214</v>
-      </c>
-      <c r="B15" s="61"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="F15" s="15" t="s">
+      <c r="H15" s="98"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="77"/>
+      <c r="B16" s="77"/>
+      <c r="C16" s="77"/>
+      <c r="D16" s="77"/>
+      <c r="F16" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="G15" s="46">
+      <c r="G16" s="99">
         <f>AVERAGE(Alice_ROI_Analysis!N:N)</f>
         <v>0.43133482816833491</v>
       </c>
-      <c r="H15" s="45"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A16" s="61"/>
-      <c r="B16" s="61"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="F16" s="15" t="s">
+      <c r="H16" s="98"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="F17" s="96" t="s">
         <v>171</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G17" s="100">
         <f>COUNTIF(Alice_ROI_Analysis!N:N, "&gt;0") / 100</f>
         <v>0.89</v>
       </c>
-      <c r="H16" s="45"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="F17" s="15" t="s">
+      <c r="H17" s="98"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A18" s="76" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="77"/>
+      <c r="C18" s="77"/>
+      <c r="D18" s="77"/>
+      <c r="F18" s="96" t="s">
         <v>172</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G18" s="101">
         <f>SUM(Alice_ROI_Analysis!H:H)</f>
         <v>66653.081500000029</v>
       </c>
-      <c r="H17" s="45" t="s">
+      <c r="H18" s="98" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" s="59" t="s">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A19" s="77"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
+      <c r="F19" s="96" t="s">
+        <v>193</v>
+      </c>
+      <c r="G19" s="102">
+        <f>G15/G18</f>
+        <v>2.607334148787416</v>
+      </c>
+      <c r="H19" s="98" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="77" t="s">
+        <v>216</v>
+      </c>
+      <c r="B21" s="76"/>
+      <c r="C21" s="76"/>
+      <c r="D21" s="76"/>
+      <c r="F21" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="G21" s="13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" s="76"/>
+      <c r="B22" s="76"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="F22" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="G22" s="14" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A24" s="79" t="s">
         <v>215</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="F18" s="15" t="s">
+      <c r="B24" s="80"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="80"/>
+    </row>
+    <row r="25" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="80"/>
+      <c r="B25" s="80"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="80"/>
+    </row>
+    <row r="26" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+    </row>
+    <row r="27" spans="1:8" ht="23" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="103" t="s">
         <v>194</v>
       </c>
-      <c r="G18" s="77">
-        <f>G14/G17</f>
-        <v>2.607334148787416</v>
-      </c>
-      <c r="H18" s="45" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-    </row>
-    <row r="21" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="61" t="s">
-        <v>217</v>
-      </c>
-      <c r="B21" s="59"/>
-      <c r="C21" s="59"/>
-      <c r="D21" s="59"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A22" s="59"/>
-      <c r="B22" s="59"/>
-      <c r="C22" s="59"/>
-      <c r="D22" s="59"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="71" t="s">
-        <v>216</v>
-      </c>
-      <c r="B24" s="62"/>
-      <c r="C24" s="62"/>
-      <c r="D24" s="62"/>
-    </row>
-    <row r="25" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="62"/>
-      <c r="B25" s="62"/>
-      <c r="C25" s="62"/>
-      <c r="D25" s="62"/>
-    </row>
-    <row r="26" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23"/>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-    </row>
-    <row r="27" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="60" t="s">
+      <c r="B27" s="103"/>
+      <c r="C27" s="103"/>
+      <c r="D27" s="103"/>
+    </row>
+    <row r="28" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="76" t="s">
         <v>195</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="60"/>
-    </row>
-    <row r="28" spans="1:8" ht="17" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="59" t="s">
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A29" s="77"/>
+      <c r="B29" s="77"/>
+      <c r="C29" s="77"/>
+      <c r="D29" s="77"/>
+    </row>
+    <row r="31" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="76" t="s">
         <v>196</v>
       </c>
-      <c r="B28" s="61"/>
-      <c r="C28" s="61"/>
-      <c r="D28" s="61"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A29" s="61"/>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-    </row>
-    <row r="31" spans="1:8" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="B31" s="59"/>
-      <c r="C31" s="59"/>
-      <c r="D31" s="59"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" s="59"/>
-      <c r="B32" s="59"/>
-      <c r="C32" s="59"/>
-      <c r="D32" s="59"/>
+      <c r="A32" s="76"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="76"/>
+      <c r="D32" s="76"/>
     </row>
     <row r="34" spans="1:4" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="59"/>
-      <c r="B34" s="59"/>
-      <c r="C34" s="59"/>
-      <c r="D34" s="59"/>
+      <c r="A34" s="76"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="76"/>
+      <c r="D34" s="76"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="59"/>
-      <c r="B35" s="59"/>
-      <c r="C35" s="59"/>
-      <c r="D35" s="59"/>
+      <c r="A35" s="76"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
     </row>
   </sheetData>
   <scenarios current="0" show="0" sqref="G8">
@@ -4871,20 +4946,21 @@
       <inputCells r="G11" val="3"/>
     </scenario>
   </scenarios>
-  <mergeCells count="13">
-    <mergeCell ref="A15:D16"/>
-    <mergeCell ref="A14:D14"/>
-    <mergeCell ref="A18:D19"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="F13:O13"/>
-    <mergeCell ref="A4:D6"/>
+  <mergeCells count="14">
+    <mergeCell ref="A3:D6"/>
+    <mergeCell ref="A8:D10"/>
+    <mergeCell ref="F14:I14"/>
     <mergeCell ref="A21:D22"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A28:D29"/>
     <mergeCell ref="A31:D32"/>
     <mergeCell ref="A34:D35"/>
     <mergeCell ref="A24:D25"/>
+    <mergeCell ref="A15:D16"/>
+    <mergeCell ref="A14:D14"/>
+    <mergeCell ref="A18:D19"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4903,7 +4979,7 @@
     <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.1640625" style="7" customWidth="1"/>
     <col min="10" max="11" width="10.83203125" style="7"/>
-    <col min="14" max="14" width="10.83203125" style="70"/>
+    <col min="14" max="14" width="10.83203125" style="53"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -4911,7 +4987,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C1" t="s">
         <v>103</v>
@@ -4923,35 +4999,35 @@
         <v>190</v>
       </c>
       <c r="F1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G1" t="s">
         <v>126</v>
       </c>
       <c r="H1" t="s">
+        <v>202</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>203</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>204</v>
       </c>
       <c r="J1" s="7" t="s">
         <v>167</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="L1" t="s">
         <v>205</v>
-      </c>
-      <c r="L1" t="s">
-        <v>206</v>
       </c>
       <c r="M1" t="s">
         <v>161</v>
       </c>
-      <c r="N1" s="70" t="s">
-        <v>207</v>
+      <c r="N1" s="53" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="69" t="s">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
       <c r="B2">
@@ -4966,7 +5042,7 @@
       <c r="E2">
         <v>1249.0802376947249</v>
       </c>
-      <c r="F2" s="69" t="s">
+      <c r="F2" t="s">
         <v>5</v>
       </c>
       <c r="G2">
@@ -4995,13 +5071,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1306.9186975909088</v>
       </c>
-      <c r="N2" s="70">
+      <c r="N2" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.46502437309940747</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3">
@@ -5016,7 +5092,7 @@
       <c r="E3">
         <v>2401.4286128198323</v>
       </c>
-      <c r="F3" s="69" t="s">
+      <c r="F3" t="s">
         <v>2</v>
       </c>
       <c r="G3">
@@ -5045,13 +5121,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3898.8371549557341</v>
       </c>
-      <c r="N3" s="70">
+      <c r="N3" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.72157735777076981</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="69" t="s">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
       <c r="B4">
@@ -5066,7 +5142,7 @@
       <c r="E4">
         <v>1963.9878836228104</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" t="s">
         <v>5</v>
       </c>
       <c r="G4">
@@ -5095,13 +5171,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2915.2741731513229</v>
       </c>
-      <c r="N4" s="70">
+      <c r="N4" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.65971761898013603</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="69" t="s">
+      <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5">
@@ -5116,7 +5192,7 @@
       <c r="E5">
         <v>1697.3169683940732</v>
       </c>
-      <c r="F5" s="69" t="s">
+      <c r="F5" t="s">
         <v>5</v>
       </c>
       <c r="G5">
@@ -5145,13 +5221,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2313.8345366644426</v>
       </c>
-      <c r="N5" s="70">
+      <c r="N5" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.60588029480268268</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="69" t="s">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
       <c r="B6">
@@ -5166,7 +5242,7 @@
       <c r="E6">
         <v>812.03728088487298</v>
       </c>
-      <c r="F6" s="69" t="s">
+      <c r="F6" t="s">
         <v>2</v>
       </c>
       <c r="G6">
@@ -5195,13 +5271,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>321.41952421318661</v>
       </c>
-      <c r="N6" s="70">
+      <c r="N6" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.17591941310485282</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="69" t="s">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7">
@@ -5216,7 +5292,7 @@
       <c r="E7">
         <v>811.98904067240528</v>
       </c>
-      <c r="F7" s="69" t="s">
+      <c r="F7" t="s">
         <v>5</v>
       </c>
       <c r="G7">
@@ -5245,13 +5321,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>323.26840595735621</v>
       </c>
-      <c r="N7" s="70">
+      <c r="N7" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.17694185499496604</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="69" t="s">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8">
@@ -5266,7 +5342,7 @@
       <c r="E8">
         <v>616.16722433639893</v>
       </c>
-      <c r="F8" s="69" t="s">
+      <c r="F8" t="s">
         <v>5</v>
       </c>
       <c r="G8">
@@ -5295,13 +5371,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-119.14322802088009</v>
       </c>
-      <c r="N8" s="70">
+      <c r="N8" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-8.5938595393623474E-2</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="69" t="s">
+      <c r="A9" t="s">
         <v>10</v>
       </c>
       <c r="B9">
@@ -5316,7 +5392,7 @@
       <c r="E9">
         <v>2232.3522915498702</v>
       </c>
-      <c r="F9" s="69" t="s">
+      <c r="F9" t="s">
         <v>2</v>
       </c>
       <c r="G9">
@@ -5345,13 +5421,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3520.5151537649854</v>
       </c>
-      <c r="N9" s="70">
+      <c r="N9" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.700907920132539</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="69" t="s">
+      <c r="A10" t="s">
         <v>11</v>
       </c>
       <c r="B10">
@@ -5366,7 +5442,7 @@
       <c r="E10">
         <v>1702.2300234864176</v>
       </c>
-      <c r="F10" s="69" t="s">
+      <c r="F10" t="s">
         <v>2</v>
       </c>
       <c r="G10">
@@ -5395,13 +5471,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2327.5146895111066</v>
       </c>
-      <c r="N10" s="70">
+      <c r="N10" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.60770340015348778</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="69" t="s">
+      <c r="A11" t="s">
         <v>12</v>
       </c>
       <c r="B11">
@@ -5416,7 +5492,7 @@
       <c r="E11">
         <v>1916.145155592091</v>
       </c>
-      <c r="F11" s="69" t="s">
+      <c r="F11" t="s">
         <v>2</v>
       </c>
       <c r="G11">
@@ -5445,13 +5521,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2810.9704623044272</v>
       </c>
-      <c r="N11" s="70">
+      <c r="N11" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.65199664118483391</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="69" t="s">
+      <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12">
@@ -5466,7 +5542,7 @@
       <c r="E12">
         <v>541.16898859160494</v>
       </c>
-      <c r="F12" s="69" t="s">
+      <c r="F12" t="s">
         <v>2</v>
       </c>
       <c r="G12">
@@ -5495,13 +5571,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-285.46823622444435</v>
       </c>
-      <c r="N12" s="70">
+      <c r="N12" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-0.23444575415435545</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="69" t="s">
+      <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13">
@@ -5516,7 +5592,7 @@
       <c r="E13">
         <v>2439.8197043239888</v>
       </c>
-      <c r="F13" s="69" t="s">
+      <c r="F13" t="s">
         <v>2</v>
       </c>
       <c r="G13">
@@ -5545,13 +5621,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3987.6477913956414</v>
       </c>
-      <c r="N13" s="70">
+      <c r="N13" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.72640117798294734</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="69" t="s">
+      <c r="A14" t="s">
         <v>15</v>
       </c>
       <c r="B14">
@@ -5566,7 +5642,7 @@
       <c r="E14">
         <v>2164.885281600843</v>
       </c>
-      <c r="F14" s="69" t="s">
+      <c r="F14" t="s">
         <v>2</v>
       </c>
       <c r="G14">
@@ -5595,13 +5671,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3370.6209363796747</v>
       </c>
-      <c r="N14" s="70">
+      <c r="N14" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.69197835203273628</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="69" t="s">
+      <c r="A15" t="s">
         <v>16</v>
       </c>
       <c r="B15">
@@ -5616,7 +5692,7 @@
       <c r="E15">
         <v>924.6782213565524</v>
       </c>
-      <c r="F15" s="69" t="s">
+      <c r="F15" t="s">
         <v>2</v>
       </c>
       <c r="G15">
@@ -5645,13 +5721,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>578.64448749668736</v>
       </c>
-      <c r="N15" s="70">
+      <c r="N15" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.27812413208890713</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="69" t="s">
+      <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16">
@@ -5666,7 +5742,7 @@
       <c r="E16">
         <v>863.6499344142012</v>
       </c>
-      <c r="F16" s="69" t="s">
+      <c r="F16" t="s">
         <v>2</v>
       </c>
       <c r="G16">
@@ -5695,13 +5771,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>439.4590568763972</v>
       </c>
-      <c r="N16" s="70">
+      <c r="N16" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.2261508148228932</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="69" t="s">
+      <c r="A17" t="s">
         <v>18</v>
       </c>
       <c r="B17">
@@ -5716,7 +5792,7 @@
       <c r="E17">
         <v>866.80901970686762</v>
       </c>
-      <c r="F17" s="69" t="s">
+      <c r="F17" t="s">
         <v>5</v>
       </c>
       <c r="G17">
@@ -5745,13 +5821,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>445.64430600711876</v>
       </c>
-      <c r="N17" s="70">
+      <c r="N17" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.22849800994242545</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A18" s="69" t="s">
+      <c r="A18" t="s">
         <v>19</v>
       </c>
       <c r="B18">
@@ -5766,7 +5842,7 @@
       <c r="E18">
         <v>1108.4844859190755</v>
       </c>
-      <c r="F18" s="69" t="s">
+      <c r="F18" t="s">
         <v>2</v>
       </c>
       <c r="G18">
@@ -5795,13 +5871,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>992.32641442903105</v>
       </c>
-      <c r="N18" s="70">
+      <c r="N18" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.39787111824373855</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="69" t="s">
+      <c r="A19" t="s">
         <v>20</v>
       </c>
       <c r="B19">
@@ -5816,7 +5892,7 @@
       <c r="E19">
         <v>1549.5128632644758</v>
       </c>
-      <c r="F19" s="69" t="s">
+      <c r="F19" t="s">
         <v>2</v>
       </c>
       <c r="G19">
@@ -5845,13 +5921,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1985.083259011737</v>
       </c>
-      <c r="N19" s="70">
+      <c r="N19" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.56937844605479204</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" s="69" t="s">
+      <c r="A20" t="s">
         <v>21</v>
       </c>
       <c r="B20">
@@ -5866,7 +5942,7 @@
       <c r="E20">
         <v>1363.8900372842315</v>
       </c>
-      <c r="F20" s="69" t="s">
+      <c r="F20" t="s">
         <v>2</v>
       </c>
       <c r="G20">
@@ -5895,13 +5971,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1564.2131000006318</v>
       </c>
-      <c r="N20" s="70">
+      <c r="N20" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.50972278058925635</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" s="69" t="s">
+      <c r="A21" t="s">
         <v>22</v>
       </c>
       <c r="B21">
@@ -5916,7 +5992,7 @@
       <c r="E21">
         <v>1082.4582803960841</v>
       </c>
-      <c r="F21" s="69" t="s">
+      <c r="F21" t="s">
         <v>5</v>
       </c>
       <c r="G21">
@@ -5945,13 +6021,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>930.0238820023003</v>
       </c>
-      <c r="N21" s="70">
+      <c r="N21" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.38185670066224681</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" s="69" t="s">
+      <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22">
@@ -5966,7 +6042,7 @@
       <c r="E22">
         <v>1723.7057894447589</v>
       </c>
-      <c r="F22" s="69" t="s">
+      <c r="F22" t="s">
         <v>2</v>
       </c>
       <c r="G22">
@@ -5995,13 +6071,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2375.1230218062628</v>
       </c>
-      <c r="N22" s="70">
+      <c r="N22" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.61240742960776873</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" s="69" t="s">
+      <c r="A23" t="s">
         <v>24</v>
       </c>
       <c r="B23">
@@ -6016,7 +6092,7 @@
       <c r="E23">
         <v>778.98772130408372</v>
       </c>
-      <c r="F23" s="69" t="s">
+      <c r="F23" t="s">
         <v>5</v>
       </c>
       <c r="G23">
@@ -6045,13 +6121,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>248.77526682307735</v>
       </c>
-      <c r="N23" s="70">
+      <c r="N23" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.14193649300351482</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" s="69" t="s">
+      <c r="A24" t="s">
         <v>25</v>
       </c>
       <c r="B24">
@@ -6066,7 +6142,7 @@
       <c r="E24">
         <v>1084.2892970704363</v>
       </c>
-      <c r="F24" s="69" t="s">
+      <c r="F24" t="s">
         <v>2</v>
       </c>
       <c r="G24">
@@ -6095,13 +6171,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>938.19566229737052</v>
       </c>
-      <c r="N24" s="70">
+      <c r="N24" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.38456143672776233</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A25" s="69" t="s">
+      <c r="A25" t="s">
         <v>26</v>
       </c>
       <c r="B25">
@@ -6116,7 +6192,7 @@
       <c r="E25">
         <v>1232.7236865873831</v>
       </c>
-      <c r="F25" s="69" t="s">
+      <c r="F25" t="s">
         <v>2</v>
       </c>
       <c r="G25">
@@ -6145,13 +6221,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1270.1460764882788</v>
       </c>
-      <c r="N25" s="70">
+      <c r="N25" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.45793665966692526</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" s="69" t="s">
+      <c r="A26" t="s">
         <v>27</v>
       </c>
       <c r="B26">
@@ -6166,7 +6242,7 @@
       <c r="E26">
         <v>1412.1399684340718</v>
       </c>
-      <c r="F26" s="69" t="s">
+      <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26">
@@ -6195,13 +6271,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1676.7643367544392</v>
       </c>
-      <c r="N26" s="70">
+      <c r="N26" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.52772997774397068</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" s="69" t="s">
+      <c r="A27" t="s">
         <v>28</v>
       </c>
       <c r="B27">
@@ -6216,7 +6292,7 @@
       <c r="E27">
         <v>2070.351922786027</v>
       </c>
-      <c r="F27" s="69" t="s">
+      <c r="F27" t="s">
         <v>5</v>
       </c>
       <c r="G27">
@@ -6245,13 +6321,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3153.6525396018942</v>
       </c>
-      <c r="N27" s="70">
+      <c r="N27" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.67699763287008785</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" s="69" t="s">
+      <c r="A28" t="s">
         <v>29</v>
       </c>
       <c r="B28">
@@ -6266,7 +6342,7 @@
       <c r="E28">
         <v>899.34756431671951</v>
       </c>
-      <c r="F28" s="69" t="s">
+      <c r="F28" t="s">
         <v>2</v>
       </c>
       <c r="G28">
@@ -6295,13 +6371,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>521.66725026817448</v>
       </c>
-      <c r="N28" s="70">
+      <c r="N28" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.25780034374858146</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" s="69" t="s">
+      <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29">
@@ -6316,7 +6392,7 @@
       <c r="E29">
         <v>1528.4688768272233</v>
       </c>
-      <c r="F29" s="69" t="s">
+      <c r="F29" t="s">
         <v>2</v>
       </c>
       <c r="G29">
@@ -6345,13 +6421,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1937.4522661945857</v>
       </c>
-      <c r="N29" s="70">
+      <c r="N29" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.56336763485424857</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A30" s="69" t="s">
+      <c r="A30" t="s">
         <v>31</v>
       </c>
       <c r="B30">
@@ -6366,7 +6442,7 @@
       <c r="E30">
         <v>1684.8291377240848</v>
       </c>
-      <c r="F30" s="69" t="s">
+      <c r="F30" t="s">
         <v>5</v>
       </c>
       <c r="G30">
@@ -6395,13 +6471,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2286.1979421014134</v>
       </c>
-      <c r="N30" s="70">
+      <c r="N30" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.60308072285588277</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A31" s="69" t="s">
+      <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31">
@@ -6416,7 +6492,7 @@
       <c r="E31">
         <v>592.9008254399954</v>
       </c>
-      <c r="F31" s="69" t="s">
+      <c r="F31" t="s">
         <v>5</v>
       </c>
       <c r="G31">
@@ -6445,13 +6521,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-170.30271887112167</v>
       </c>
-      <c r="N31" s="70">
+      <c r="N31" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-0.12766063737537217</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A32" s="69" t="s">
+      <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
@@ -6466,7 +6542,7 @@
       <c r="E32">
         <v>1715.0897038028768</v>
       </c>
-      <c r="F32" s="69" t="s">
+      <c r="F32" t="s">
         <v>2</v>
       </c>
       <c r="G32">
@@ -6495,13 +6571,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2357.5757757786951</v>
       </c>
-      <c r="N32" s="70">
+      <c r="N32" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.61093682364154178</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A33" s="69" t="s">
+      <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33">
@@ -6516,7 +6592,7 @@
       <c r="E33">
         <v>841.04824737458307</v>
       </c>
-      <c r="F33" s="69" t="s">
+      <c r="F33" t="s">
         <v>5</v>
       </c>
       <c r="G33">
@@ -6545,13 +6621,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>390.99730825947859</v>
       </c>
-      <c r="N33" s="70">
+      <c r="N33" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.20661903997911923</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A34" s="69" t="s">
+      <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34">
@@ -6566,7 +6642,7 @@
       <c r="E34">
         <v>630.10318597055903</v>
       </c>
-      <c r="F34" s="69" t="s">
+      <c r="F34" t="s">
         <v>2</v>
       </c>
       <c r="G34">
@@ -6595,13 +6671,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-84.827357121797604</v>
       </c>
-      <c r="N34" s="70">
+      <c r="N34" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-5.9833132809217968E-2</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A35" s="69" t="s">
+      <c r="A35" t="s">
         <v>36</v>
       </c>
       <c r="B35">
@@ -6616,7 +6692,7 @@
       <c r="E35">
         <v>2397.7710745066665</v>
       </c>
-      <c r="F35" s="69" t="s">
+      <c r="F35" t="s">
         <v>5</v>
       </c>
       <c r="G35">
@@ -6645,13 +6721,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3893.0589787511108</v>
       </c>
-      <c r="N35" s="70">
+      <c r="N35" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.72160701803298155</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A36" s="69" t="s">
+      <c r="A36" t="s">
         <v>37</v>
       </c>
       <c r="B36">
@@ -6666,7 +6742,7 @@
       <c r="E36">
         <v>2431.2640661491187</v>
       </c>
-      <c r="F36" s="69" t="s">
+      <c r="F36" t="s">
         <v>5</v>
       </c>
       <c r="G36">
@@ -6695,13 +6771,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3968.4536238355167</v>
       </c>
-      <c r="N36" s="70">
+      <c r="N36" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.72544862185321368</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A37" s="69" t="s">
+      <c r="A37" t="s">
         <v>38</v>
       </c>
       <c r="B37">
@@ -6716,7 +6792,7 @@
       <c r="E37">
         <v>2116.7946962329224</v>
       </c>
-      <c r="F37" s="69" t="s">
+      <c r="F37" t="s">
         <v>5</v>
       </c>
       <c r="G37">
@@ -6745,13 +6821,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3261.2916015240753</v>
       </c>
-      <c r="N37" s="70">
+      <c r="N37" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.68474422039614169</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A38" s="69" t="s">
+      <c r="A38" t="s">
         <v>39</v>
       </c>
       <c r="B38">
@@ -6766,7 +6842,7 @@
       <c r="E38">
         <v>1109.2275383467413</v>
       </c>
-      <c r="F38" s="69" t="s">
+      <c r="F38" t="s">
         <v>2</v>
       </c>
       <c r="G38">
@@ -6795,13 +6871,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>992.78970294683495</v>
       </c>
-      <c r="N38" s="70">
+      <c r="N38" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.39779022132286868</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A39" s="69" t="s">
+      <c r="A39" t="s">
         <v>40</v>
       </c>
       <c r="B39">
@@ -6816,7 +6892,7 @@
       <c r="E39">
         <v>695.34422801276776</v>
       </c>
-      <c r="F39" s="69" t="s">
+      <c r="F39" t="s">
         <v>5</v>
       </c>
       <c r="G39">
@@ -6845,13 +6921,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>60.596079695393883</v>
       </c>
-      <c r="N39" s="70">
+      <c r="N39" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>3.8731307301850648E-2</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A40" s="69" t="s">
+      <c r="A40" t="s">
         <v>41</v>
       </c>
       <c r="B40">
@@ -6866,7 +6942,7 @@
       <c r="E40">
         <v>1868.4660530243141</v>
       </c>
-      <c r="F40" s="69" t="s">
+      <c r="F40" t="s">
         <v>5</v>
       </c>
       <c r="G40">
@@ -6895,13 +6971,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2700.5219726380396</v>
       </c>
-      <c r="N40" s="70">
+      <c r="N40" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.64236221251995651</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="69" t="s">
+      <c r="A41" t="s">
         <v>42</v>
       </c>
       <c r="B41">
@@ -6916,7 +6992,7 @@
       <c r="E41">
         <v>1380.3049874792025</v>
       </c>
-      <c r="F41" s="69" t="s">
+      <c r="F41" t="s">
         <v>2</v>
       </c>
       <c r="G41">
@@ -6945,13 +7021,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1600.723059050428</v>
       </c>
-      <c r="N41" s="70">
+      <c r="N41" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.51541686594086766</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="69" t="s">
+      <c r="A42" t="s">
         <v>43</v>
       </c>
       <c r="B42">
@@ -6966,7 +7042,7 @@
       <c r="E42">
         <v>744.0764696895576</v>
       </c>
-      <c r="F42" s="69" t="s">
+      <c r="F42" t="s">
         <v>2</v>
       </c>
       <c r="G42">
@@ -6995,13 +7071,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>171.51916735706004</v>
       </c>
-      <c r="N42" s="70">
+      <c r="N42" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.10245014343671842</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A43" s="69" t="s">
+      <c r="A43" t="s">
         <v>44</v>
       </c>
       <c r="B43">
@@ -7016,7 +7092,7 @@
       <c r="E43">
         <v>1490.3538202225404</v>
       </c>
-      <c r="F43" s="69" t="s">
+      <c r="F43" t="s">
         <v>5</v>
       </c>
       <c r="G43">
@@ -7045,13 +7121,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1852.2716010562717</v>
       </c>
-      <c r="N43" s="70">
+      <c r="N43" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.5523734106098046</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="69" t="s">
+      <c r="A44" t="s">
         <v>45</v>
       </c>
       <c r="B44">
@@ -7066,7 +7142,7 @@
       <c r="E44">
         <v>568.77704223043679</v>
       </c>
-      <c r="F44" s="69" t="s">
+      <c r="F44" t="s">
         <v>5</v>
       </c>
       <c r="G44">
@@ -7095,13 +7171,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-224.87677609262846</v>
       </c>
-      <c r="N44" s="70">
+      <c r="N44" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-0.17571952874014515</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A45" s="69" t="s">
+      <c r="A45" t="s">
         <v>46</v>
       </c>
       <c r="B45">
@@ -7116,7 +7192,7 @@
       <c r="E45">
         <v>2318.6408041575642</v>
       </c>
-      <c r="F45" s="69" t="s">
+      <c r="F45" t="s">
         <v>2</v>
       </c>
       <c r="G45">
@@ -7145,13 +7221,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3714.7087354656305</v>
       </c>
-      <c r="N45" s="70">
+      <c r="N45" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.71204718611290074</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="69" t="s">
+      <c r="A46" t="s">
         <v>47</v>
       </c>
       <c r="B46">
@@ -7166,7 +7242,7 @@
       <c r="E46">
         <v>1017.5599632000338</v>
       </c>
-      <c r="F46" s="69" t="s">
+      <c r="F46" t="s">
         <v>2</v>
       </c>
       <c r="G46">
@@ -7195,13 +7271,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>787.61939220007594</v>
       </c>
-      <c r="N46" s="70">
+      <c r="N46" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.34401222125444386</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="69" t="s">
+      <c r="A47" t="s">
         <v>48</v>
       </c>
       <c r="B47">
@@ -7216,7 +7292,7 @@
       <c r="E47">
         <v>1825.0445687079639</v>
       </c>
-      <c r="F47" s="69" t="s">
+      <c r="F47" t="s">
         <v>2</v>
       </c>
       <c r="G47">
@@ -7245,13 +7321,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2605.7777951484745</v>
       </c>
-      <c r="N47" s="70">
+      <c r="N47" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.63457270269861077</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" s="69" t="s">
+      <c r="A48" t="s">
         <v>49</v>
       </c>
       <c r="B48">
@@ -7266,7 +7342,7 @@
       <c r="E48">
         <v>1123.422152178822</v>
       </c>
-      <c r="F48" s="69" t="s">
+      <c r="F48" t="s">
         <v>2</v>
       </c>
       <c r="G48">
@@ -7295,13 +7371,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1024.6889507356827</v>
       </c>
-      <c r="N48" s="70">
+      <c r="N48" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.40538395166484986</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="69" t="s">
+      <c r="A49" t="s">
         <v>50</v>
       </c>
       <c r="B49">
@@ -7316,7 +7392,7 @@
       <c r="E49">
         <v>1540.1360423556216</v>
       </c>
-      <c r="F49" s="69" t="s">
+      <c r="F49" t="s">
         <v>5</v>
       </c>
       <c r="G49">
@@ -7345,13 +7421,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1964.0079480779264</v>
       </c>
-      <c r="N49" s="70">
+      <c r="N49" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.56676319322602675</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="69" t="s">
+      <c r="A50" t="s">
         <v>51</v>
       </c>
       <c r="B50">
@@ -7366,7 +7442,7 @@
       <c r="E50">
         <v>1593.4205586865594</v>
       </c>
-      <c r="F50" s="69" t="s">
+      <c r="F50" t="s">
         <v>5</v>
       </c>
       <c r="G50">
@@ -7395,13 +7471,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2079.8686531558697</v>
       </c>
-      <c r="N50" s="70">
+      <c r="N50" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.58012686169383776</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" s="69" t="s">
+      <c r="A51" t="s">
         <v>52</v>
       </c>
       <c r="B51">
@@ -7416,7 +7492,7 @@
       <c r="E51">
         <v>869.70891105105409</v>
       </c>
-      <c r="F51" s="69" t="s">
+      <c r="F51" t="s">
         <v>2</v>
       </c>
       <c r="G51">
@@ -7445,13 +7521,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>453.56758819820493</v>
       </c>
-      <c r="N51" s="70">
+      <c r="N51" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.23178513200599385</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="69" t="s">
+      <c r="A52" t="s">
         <v>53</v>
       </c>
       <c r="B52">
@@ -7466,7 +7542,7 @@
       <c r="E52">
         <v>2439.169255529117</v>
       </c>
-      <c r="F52" s="69" t="s">
+      <c r="F52" t="s">
         <v>5</v>
       </c>
       <c r="G52">
@@ -7495,13 +7571,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3988.1024266071795</v>
       </c>
-      <c r="N52" s="70">
+      <c r="N52" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.72667772577203593</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" s="69" t="s">
+      <c r="A53" t="s">
         <v>54</v>
       </c>
       <c r="B53">
@@ -7516,7 +7592,7 @@
       <c r="E53">
         <v>2050.2656467222291</v>
       </c>
-      <c r="F53" s="69" t="s">
+      <c r="F53" t="s">
         <v>2</v>
       </c>
       <c r="G53">
@@ -7545,13 +7621,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3108.0984845694602</v>
       </c>
-      <c r="N53" s="70">
+      <c r="N53" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.67375518214505936</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="69" t="s">
+      <c r="A54" t="s">
         <v>55</v>
       </c>
       <c r="B54">
@@ -7566,7 +7642,7 @@
       <c r="E54">
         <v>2378.9978831283784</v>
       </c>
-      <c r="F54" s="69" t="s">
+      <c r="F54" t="s">
         <v>2</v>
       </c>
       <c r="G54">
@@ -7595,13 +7671,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3851.2584303721842</v>
       </c>
-      <c r="N54" s="70">
+      <c r="N54" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.71949219696148059</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="69" t="s">
+      <c r="A55" t="s">
         <v>56</v>
       </c>
       <c r="B55">
@@ -7616,7 +7692,7 @@
       <c r="E55">
         <v>2289.6547008552975</v>
       </c>
-      <c r="F55" s="69" t="s">
+      <c r="F55" t="s">
         <v>2</v>
       </c>
       <c r="G55">
@@ -7645,13 +7721,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3650.8292919244195</v>
       </c>
-      <c r="N55" s="70">
+      <c r="N55" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.7086617889609016</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="69" t="s">
+      <c r="A56" t="s">
         <v>57</v>
       </c>
       <c r="B56">
@@ -7666,7 +7742,7 @@
       <c r="E56">
         <v>1695.7999576221705</v>
       </c>
-      <c r="F56" s="69" t="s">
+      <c r="F56" t="s">
         <v>5</v>
       </c>
       <c r="G56">
@@ -7695,13 +7771,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2312.3033496498833</v>
       </c>
-      <c r="N56" s="70">
+      <c r="N56" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.60602099498998985</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="69" t="s">
+      <c r="A57" t="s">
         <v>58</v>
       </c>
       <c r="B57">
@@ -7716,7 +7792,7 @@
       <c r="E57">
         <v>2343.7484700462337</v>
       </c>
-      <c r="F57" s="69" t="s">
+      <c r="F57" t="s">
         <v>5</v>
       </c>
       <c r="G57">
@@ -7745,13 +7821,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3772.7244248262482</v>
       </c>
-      <c r="N57" s="70">
+      <c r="N57" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.71542080238704608</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="69" t="s">
+      <c r="A58" t="s">
         <v>59</v>
       </c>
       <c r="B58">
@@ -7766,7 +7842,7 @@
       <c r="E58">
         <v>676.98500410383895</v>
       </c>
-      <c r="F58" s="69" t="s">
+      <c r="F58" t="s">
         <v>2</v>
       </c>
       <c r="G58">
@@ -7795,13 +7871,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>17.620153678082033</v>
       </c>
-      <c r="N58" s="70">
+      <c r="N58" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>1.1567729513960878E-2</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="69" t="s">
+      <c r="A59" t="s">
         <v>60</v>
       </c>
       <c r="B59">
@@ -7816,7 +7892,7 @@
       <c r="E59">
         <v>891.96572483829038</v>
       </c>
-      <c r="F59" s="69" t="s">
+      <c r="F59" t="s">
         <v>2</v>
       </c>
       <c r="G59">
@@ -7845,13 +7921,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>504.41100310837555</v>
       </c>
-      <c r="N59" s="70">
+      <c r="N59" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.25133551862523673</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="69" t="s">
+      <c r="A60" t="s">
         <v>61</v>
       </c>
       <c r="B60">
@@ -7866,7 +7942,7 @@
       <c r="E60">
         <v>590.4545778210761</v>
       </c>
-      <c r="F60" s="69" t="s">
+      <c r="F60" t="s">
         <v>5</v>
       </c>
       <c r="G60">
@@ -7895,13 +7971,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-174.78749990257893</v>
       </c>
-      <c r="N60" s="70">
+      <c r="N60" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-0.1315652993608854</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" s="69" t="s">
+      <c r="A61" t="s">
         <v>62</v>
       </c>
       <c r="B61">
@@ -7916,7 +7992,7 @@
       <c r="E61">
         <v>1150.6606615265289</v>
       </c>
-      <c r="F61" s="69" t="s">
+      <c r="F61" t="s">
         <v>2</v>
       </c>
       <c r="G61">
@@ -7945,13 +8021,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1086.3754517680231</v>
       </c>
-      <c r="N61" s="70">
+      <c r="N61" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.41961418362783715</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62" s="69" t="s">
+      <c r="A62" t="s">
         <v>63</v>
       </c>
       <c r="B62">
@@ -7966,7 +8042,7 @@
       <c r="E62">
         <v>1277.354579378964</v>
       </c>
-      <c r="F62" s="69" t="s">
+      <c r="F62" t="s">
         <v>2</v>
       </c>
       <c r="G62">
@@ -7995,13 +8071,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1370.7478058248912</v>
       </c>
-      <c r="N62" s="70">
+      <c r="N62" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.47693980737085689</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="69" t="s">
+      <c r="A63" t="s">
         <v>64</v>
       </c>
       <c r="B63">
@@ -8016,7 +8092,7 @@
       <c r="E63">
         <v>1042.6980635477919</v>
       </c>
-      <c r="F63" s="69" t="s">
+      <c r="F63" t="s">
         <v>2</v>
       </c>
       <c r="G63">
@@ -8045,13 +8121,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>843.74678076030955</v>
       </c>
-      <c r="N63" s="70">
+      <c r="N63" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.35964252964167537</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" s="69" t="s">
+      <c r="A64" t="s">
         <v>65</v>
       </c>
       <c r="B64">
@@ -8066,7 +8142,7 @@
       <c r="E64">
         <v>2157.4750183038582</v>
       </c>
-      <c r="F64" s="69" t="s">
+      <c r="F64" t="s">
         <v>5</v>
       </c>
       <c r="G64">
@@ -8095,13 +8171,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3351.13083007257</v>
       </c>
-      <c r="N64" s="70">
+      <c r="N64" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.69034008152880855</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="69" t="s">
+      <c r="A65" t="s">
         <v>66</v>
       </c>
       <c r="B65">
@@ -8116,7 +8192,7 @@
       <c r="E65">
         <v>1213.5066533871786</v>
       </c>
-      <c r="F65" s="69" t="s">
+      <c r="F65" t="s">
         <v>2</v>
       </c>
       <c r="G65">
@@ -8145,13 +8221,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1225.6714851211523</v>
       </c>
-      <c r="N65" s="70">
+      <c r="N65" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.44889979033535898</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="69" t="s">
+      <c r="A66" t="s">
         <v>67</v>
       </c>
       <c r="B66">
@@ -8166,7 +8242,7 @@
       <c r="E66">
         <v>1061.8690193747616</v>
       </c>
-      <c r="F66" s="69" t="s">
+      <c r="F66" t="s">
         <v>2</v>
       </c>
       <c r="G66">
@@ -8195,13 +8271,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>888.81181025988008</v>
       </c>
-      <c r="N66" s="70">
+      <c r="N66" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.37201148542709089</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="69" t="s">
+      <c r="A67" t="s">
         <v>68</v>
       </c>
       <c r="B67">
@@ -8216,7 +8292,7 @@
       <c r="E67">
         <v>1585.392166316497</v>
       </c>
-      <c r="F67" s="69" t="s">
+      <c r="F67" t="s">
         <v>2</v>
       </c>
       <c r="G67">
@@ -8245,13 +8321,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2065.7015858787845</v>
       </c>
-      <c r="N67" s="70">
+      <c r="N67" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.57909305547850365</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" s="69" t="s">
+      <c r="A68" t="s">
         <v>69</v>
       </c>
       <c r="B68">
@@ -8266,7 +8342,7 @@
       <c r="E68">
         <v>781.84844994952527</v>
       </c>
-      <c r="F68" s="69" t="s">
+      <c r="F68" t="s">
         <v>5</v>
       </c>
       <c r="G68">
@@ -8295,13 +8371,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>256.30522960865414</v>
       </c>
-      <c r="N68" s="70">
+      <c r="N68" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.14569759061232149</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" s="69" t="s">
+      <c r="A69" t="s">
         <v>70</v>
       </c>
       <c r="B69">
@@ -8316,7 +8392,7 @@
       <c r="E69">
         <v>2104.393961508079</v>
       </c>
-      <c r="F69" s="69" t="s">
+      <c r="F69" t="s">
         <v>5</v>
       </c>
       <c r="G69">
@@ -8345,13 +8421,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3230.9264295042885</v>
       </c>
-      <c r="N69" s="70">
+      <c r="N69" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.68236619581099922</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" s="69" t="s">
+      <c r="A70" t="s">
         <v>71</v>
       </c>
       <c r="B70">
@@ -8366,7 +8442,7 @@
       <c r="E70">
         <v>649.10128735954163</v>
       </c>
-      <c r="F70" s="69" t="s">
+      <c r="F70" t="s">
         <v>5</v>
       </c>
       <c r="G70">
@@ -8395,13 +8471,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-42.789906774364454</v>
       </c>
-      <c r="N70" s="70">
+      <c r="N70" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-2.9298565130757358E-2</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71" s="69" t="s">
+      <c r="A71" t="s">
         <v>72</v>
       </c>
       <c r="B71">
@@ -8416,7 +8492,7 @@
       <c r="E71">
         <v>2473.7738732010348</v>
       </c>
-      <c r="F71" s="69" t="s">
+      <c r="F71" t="s">
         <v>2</v>
       </c>
       <c r="G71">
@@ -8445,13 +8521,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>4061.5090369245499</v>
       </c>
-      <c r="N71" s="70">
+      <c r="N71" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.7297009427891743</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A72" s="69" t="s">
+      <c r="A72" t="s">
         <v>73</v>
       </c>
       <c r="B72">
@@ -8466,7 +8542,7 @@
       <c r="E72">
         <v>2044.4895385933148</v>
       </c>
-      <c r="F72" s="69" t="s">
+      <c r="F72" t="s">
         <v>5</v>
       </c>
       <c r="G72">
@@ -8495,13 +8571,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3096.990123501625</v>
       </c>
-      <c r="N72" s="70">
+      <c r="N72" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.67324387281367715</v>
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A73" s="69" t="s">
+      <c r="A73" t="s">
         <v>74</v>
       </c>
       <c r="B73">
@@ -8516,7 +8592,7 @@
       <c r="E73">
         <v>897.43136306834481</v>
       </c>
-      <c r="F73" s="69" t="s">
+      <c r="F73" t="s">
         <v>5</v>
       </c>
       <c r="G73">
@@ -8545,13 +8621,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>518.32291857044243</v>
       </c>
-      <c r="N73" s="70">
+      <c r="N73" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.25669455188108858</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A74" s="69" t="s">
+      <c r="A74" t="s">
         <v>75</v>
       </c>
       <c r="B74">
@@ -8566,7 +8642,7 @@
       <c r="E74">
         <v>511.04423424720483</v>
       </c>
-      <c r="F74" s="69" t="s">
+      <c r="F74" t="s">
         <v>2</v>
       </c>
       <c r="G74">
@@ -8595,13 +8671,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-354.06731627712247</v>
       </c>
-      <c r="N74" s="70">
+      <c r="N74" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-0.30792491360464225</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A75" s="69" t="s">
+      <c r="A75" t="s">
         <v>76</v>
       </c>
       <c r="B75">
@@ -8616,7 +8692,7 @@
       <c r="E75">
         <v>2130.9228569096681</v>
       </c>
-      <c r="F75" s="69" t="s">
+      <c r="F75" t="s">
         <v>5</v>
       </c>
       <c r="G75">
@@ -8645,13 +8721,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3292.3864947134198</v>
       </c>
-      <c r="N75" s="70">
+      <c r="N75" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.68668975124768106</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A76" s="69" t="s">
+      <c r="A76" t="s">
         <v>77</v>
       </c>
       <c r="B76">
@@ -8666,7 +8742,7 @@
       <c r="E76">
         <v>1913.7146876952345</v>
       </c>
-      <c r="F76" s="69" t="s">
+      <c r="F76" t="s">
         <v>2</v>
       </c>
       <c r="G76">
@@ -8695,13 +8771,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2803.1323984253886</v>
       </c>
-      <c r="N76" s="70">
+      <c r="N76" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.65100436837991116</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A77" s="69" t="s">
+      <c r="A77" t="s">
         <v>78</v>
       </c>
       <c r="B77">
@@ -8716,7 +8792,7 @@
       <c r="E77">
         <v>1958.0143360819743</v>
       </c>
-      <c r="F77" s="69" t="s">
+      <c r="F77" t="s">
         <v>2</v>
       </c>
       <c r="G77">
@@ -8745,13 +8821,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2904.368681739998</v>
       </c>
-      <c r="N77" s="70">
+      <c r="N77" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.65925488972708668</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A78" s="69" t="s">
+      <c r="A78" t="s">
         <v>79</v>
       </c>
       <c r="B78">
@@ -8766,7 +8842,7 @@
       <c r="E78">
         <v>2042.5406933718912</v>
       </c>
-      <c r="F78" s="69" t="s">
+      <c r="F78" t="s">
         <v>5</v>
       </c>
       <c r="G78">
@@ -8795,13 +8871,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3091.7874828645326</v>
       </c>
-      <c r="N78" s="70">
+      <c r="N78" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.6727541706371396</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A79" s="69" t="s">
+      <c r="A79" t="s">
         <v>80</v>
       </c>
       <c r="B79">
@@ -8816,7 +8892,7 @@
       <c r="E79">
         <v>648.08930346818067</v>
       </c>
-      <c r="F79" s="69" t="s">
+      <c r="F79" t="s">
         <v>2</v>
       </c>
       <c r="G79">
@@ -8845,13 +8921,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-45.786094418815765</v>
       </c>
-      <c r="N79" s="70">
+      <c r="N79" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-3.1399029714506851E-2</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A80" s="69" t="s">
+      <c r="A80" t="s">
         <v>81</v>
       </c>
       <c r="B80">
@@ -8866,7 +8942,7 @@
       <c r="E80">
         <v>1216.9314570885451</v>
       </c>
-      <c r="F80" s="69" t="s">
+      <c r="F80" t="s">
         <v>5</v>
       </c>
       <c r="G80">
@@ -8895,13 +8971,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1234.5208401158932</v>
       </c>
-      <c r="N80" s="70">
+      <c r="N80" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.45086839176060084</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A81" s="69" t="s">
+      <c r="A81" t="s">
         <v>82</v>
       </c>
       <c r="B81">
@@ -8916,7 +8992,7 @@
       <c r="E81">
         <v>731.73811905025946</v>
       </c>
-      <c r="F81" s="69" t="s">
+      <c r="F81" t="s">
         <v>5</v>
       </c>
       <c r="G81">
@@ -8945,13 +9021,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>142.30333341863911</v>
       </c>
-      <c r="N81" s="70">
+      <c r="N81" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>8.6432460353340651E-2</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A82" s="69" t="s">
+      <c r="A82" t="s">
         <v>83</v>
       </c>
       <c r="B82">
@@ -8966,7 +9042,7 @@
       <c r="E82">
         <v>2226.2068517511871</v>
       </c>
-      <c r="F82" s="69" t="s">
+      <c r="F82" t="s">
         <v>5</v>
       </c>
       <c r="G82">
@@ -8995,13 +9071,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3505.8772581068374</v>
       </c>
-      <c r="N82" s="70">
+      <c r="N82" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.69992043598464981</v>
       </c>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A83" s="69" t="s">
+      <c r="A83" t="s">
         <v>84</v>
       </c>
       <c r="B83">
@@ -9016,7 +9092,7 @@
       <c r="E83">
         <v>1746.5962536551158</v>
       </c>
-      <c r="F83" s="69" t="s">
+      <c r="F83" t="s">
         <v>5</v>
       </c>
       <c r="G83">
@@ -9045,13 +9121,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2424.5571073906772</v>
       </c>
-      <c r="N83" s="70">
+      <c r="N83" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.61696052213728081</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A84" s="69" t="s">
+      <c r="A84" t="s">
         <v>85</v>
       </c>
       <c r="B84">
@@ -9066,7 +9142,7 @@
       <c r="E84">
         <v>1161.7960497052984</v>
       </c>
-      <c r="F84" s="69" t="s">
+      <c r="F84" t="s">
         <v>2</v>
       </c>
       <c r="G84">
@@ -9095,13 +9171,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1112.7197846146994</v>
       </c>
-      <c r="N84" s="70">
+      <c r="N84" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.42567034603093001</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A85" s="69" t="s">
+      <c r="A85" t="s">
         <v>86</v>
       </c>
       <c r="B85">
@@ -9116,7 +9192,7 @@
       <c r="E85">
         <v>627.11670057204731</v>
       </c>
-      <c r="F85" s="69" t="s">
+      <c r="F85" t="s">
         <v>5</v>
       </c>
       <c r="G85">
@@ -9145,13 +9221,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-92.190194268449204</v>
       </c>
-      <c r="N85" s="70">
+      <c r="N85" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-6.5336196018206685E-2</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A86" s="69" t="s">
+      <c r="A86" t="s">
         <v>87</v>
       </c>
       <c r="B86">
@@ -9166,7 +9242,7 @@
       <c r="E86">
         <v>1121.9646434313245</v>
       </c>
-      <c r="F86" s="69" t="s">
+      <c r="F86" t="s">
         <v>2</v>
       </c>
       <c r="G86">
@@ -9195,13 +9271,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1023.0031810538137</v>
       </c>
-      <c r="N86" s="70">
+      <c r="N86" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.40524278829129778</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A87" s="69" t="s">
+      <c r="A87" t="s">
         <v>88</v>
       </c>
       <c r="B87">
@@ -9216,7 +9292,7 @@
       <c r="E87">
         <v>1150.3666440534942</v>
       </c>
-      <c r="F87" s="69" t="s">
+      <c r="F87" t="s">
         <v>5</v>
       </c>
       <c r="G87">
@@ -9245,13 +9321,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1085.6933080092508</v>
       </c>
-      <c r="N87" s="70">
+      <c r="N87" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.41945788467488287</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A88" s="69" t="s">
+      <c r="A88" t="s">
         <v>89</v>
       </c>
       <c r="B88">
@@ -9266,7 +9342,7 @@
       <c r="E88">
         <v>1959.2123566761279</v>
       </c>
-      <c r="F88" s="69" t="s">
+      <c r="F88" t="s">
         <v>2</v>
       </c>
       <c r="G88">
@@ -9295,13 +9371,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2903.5962425212883</v>
       </c>
-      <c r="N88" s="70">
+      <c r="N88" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.65867654136670861</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A89" s="69" t="s">
+      <c r="A89" t="s">
         <v>90</v>
       </c>
       <c r="B89">
@@ -9316,7 +9392,7 @@
       <c r="E89">
         <v>1775.1149427104262</v>
       </c>
-      <c r="F89" s="69" t="s">
+      <c r="F89" t="s">
         <v>5</v>
       </c>
       <c r="G89">
@@ -9345,13 +9421,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2489.923078876237</v>
       </c>
-      <c r="N89" s="70">
+      <c r="N89" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.62341454791137674</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A90" s="69" t="s">
+      <c r="A90" t="s">
         <v>91</v>
       </c>
       <c r="B90">
@@ -9366,7 +9442,7 @@
       <c r="E90">
         <v>2274.425485152653</v>
       </c>
-      <c r="F90" s="69" t="s">
+      <c r="F90" t="s">
         <v>2</v>
       </c>
       <c r="G90">
@@ -9395,13 +9471,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3614.1579877045806</v>
       </c>
-      <c r="N90" s="70">
+      <c r="N90" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.70624096039444606</v>
       </c>
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A91" s="69" t="s">
+      <c r="A91" t="s">
         <v>92</v>
       </c>
       <c r="B91">
@@ -9416,7 +9492,7 @@
       <c r="E91">
         <v>1444.4298503238986</v>
       </c>
-      <c r="F91" s="69" t="s">
+      <c r="F91" t="s">
         <v>2</v>
       </c>
       <c r="G91">
@@ -9445,13 +9521,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1749.4796721176608</v>
       </c>
-      <c r="N91" s="70">
+      <c r="N91" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.53830687642381925</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A92" s="69" t="s">
+      <c r="A92" t="s">
         <v>93</v>
       </c>
       <c r="B92">
@@ -9466,7 +9542,7 @@
       <c r="E92">
         <v>739.18849187660339</v>
       </c>
-      <c r="F92" s="69" t="s">
+      <c r="F92" t="s">
         <v>2</v>
       </c>
       <c r="G92">
@@ -9495,13 +9571,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>160.98417338902436</v>
       </c>
-      <c r="N92" s="70">
+      <c r="N92" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>9.6793337954423964E-2</v>
       </c>
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A93" s="69" t="s">
+      <c r="A93" t="s">
         <v>94</v>
       </c>
       <c r="B93">
@@ -9516,7 +9592,7 @@
       <c r="E93">
         <v>1926.48957444599</v>
       </c>
-      <c r="F93" s="69" t="s">
+      <c r="F93" t="s">
         <v>5</v>
       </c>
       <c r="G93">
@@ -9545,13 +9621,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2831.1122413923663</v>
       </c>
-      <c r="N93" s="70">
+      <c r="N93" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.65314244311306158</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A94" s="69" t="s">
+      <c r="A94" t="s">
         <v>95</v>
       </c>
       <c r="B94">
@@ -9566,7 +9642,7 @@
       <c r="E94">
         <v>2021.570097233795</v>
       </c>
-      <c r="F94" s="69" t="s">
+      <c r="F94" t="s">
         <v>5</v>
       </c>
       <c r="G94">
@@ -9595,13 +9671,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3047.9241765538163</v>
       </c>
-      <c r="N94" s="70">
+      <c r="N94" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.67008953546100469</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A95" s="69" t="s">
+      <c r="A95" t="s">
         <v>96</v>
       </c>
       <c r="B95">
@@ -9616,7 +9692,7 @@
       <c r="E95">
         <v>1622.5543951389925</v>
       </c>
-      <c r="F95" s="69" t="s">
+      <c r="F95" t="s">
         <v>2</v>
       </c>
       <c r="G95">
@@ -9645,13 +9721,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>2146.5877996182885</v>
       </c>
-      <c r="N95" s="70">
+      <c r="N95" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.5879858480620288</v>
       </c>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A96" s="69" t="s">
+      <c r="A96" t="s">
         <v>97</v>
       </c>
       <c r="B96">
@@ -9666,7 +9742,7 @@
       <c r="E96">
         <v>2041.9343599091219</v>
       </c>
-      <c r="F96" s="69" t="s">
+      <c r="F96" t="s">
         <v>2</v>
       </c>
       <c r="G96">
@@ -9695,13 +9771,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>3090.2455192399684</v>
       </c>
-      <c r="N96" s="70">
+      <c r="N96" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.67261831720029819</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A97" s="69" t="s">
+      <c r="A97" t="s">
         <v>98</v>
       </c>
       <c r="B97">
@@ -9716,7 +9792,7 @@
       <c r="E97">
         <v>1487.5911927287814</v>
       </c>
-      <c r="F97" s="69" t="s">
+      <c r="F97" t="s">
         <v>2</v>
       </c>
       <c r="G97">
@@ -9745,13 +9821,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1842.0313836397581</v>
       </c>
-      <c r="N97" s="70">
+      <c r="N97" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.55033978350547141</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A98" s="69" t="s">
+      <c r="A98" t="s">
         <v>99</v>
       </c>
       <c r="B98">
@@ -9766,7 +9842,7 @@
       <c r="E98">
         <v>1545.4656587639879</v>
       </c>
-      <c r="F98" s="69" t="s">
+      <c r="F98" t="s">
         <v>2</v>
       </c>
       <c r="G98">
@@ -9795,13 +9871,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1973.9307699967503</v>
       </c>
-      <c r="N98" s="70">
+      <c r="N98" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.56766228318825129</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A99" s="69" t="s">
+      <c r="A99" t="s">
         <v>100</v>
       </c>
       <c r="B99">
@@ -9816,7 +9892,7 @@
       <c r="E99">
         <v>1355.0820367170993</v>
       </c>
-      <c r="F99" s="69" t="s">
+      <c r="F99" t="s">
         <v>5</v>
       </c>
       <c r="G99">
@@ -9845,13 +9921,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>1544.3274903912516</v>
       </c>
-      <c r="N99" s="70">
+      <c r="N99" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>0.50651381607128187</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A100" s="69" t="s">
+      <c r="A100" t="s">
         <v>101</v>
       </c>
       <c r="B100">
@@ -9866,7 +9942,7 @@
       <c r="E100">
         <v>550.83825348819039</v>
       </c>
-      <c r="F100" s="69" t="s">
+      <c r="F100" t="s">
         <v>5</v>
       </c>
       <c r="G100">
@@ -9895,13 +9971,13 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>-262.34927742934951</v>
       </c>
-      <c r="N100" s="70">
+      <c r="N100" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>-0.21167680007537548</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A101" s="69" t="s">
+      <c r="A101" t="s">
         <v>102</v>
       </c>
       <c r="B101">
@@ -9916,7 +9992,7 @@
       <c r="E101">
         <v>715.78285398660887</v>
       </c>
-      <c r="F101" s="69" t="s">
+      <c r="F101" t="s">
         <v>2</v>
       </c>
       <c r="G101">
@@ -9945,7 +10021,7 @@
         <f>Alice_Master_Analysis[[#This Row],[Sortie Revenue]]-Alice_Master_Analysis[[#This Row],[Total OpEx per Sortie]]</f>
         <v>106.97833591431436</v>
       </c>
-      <c r="N101" s="70">
+      <c r="N101" s="53">
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]/Alice_Master_Analysis[[#This Row],[Sortie Revenue]]</f>
         <v>6.6425071246423162E-2</v>
       </c>
@@ -9970,23 +10046,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C1" t="s">
         <v>210</v>
-      </c>
-      <c r="C1" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="18">
+      <c r="B2" s="16">
         <v>-0.1981654888851293</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="23">
         <v>-245.30863746620756</v>
       </c>
     </row>
@@ -9994,10 +10070,10 @@
       <c r="A3" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="18">
+      <c r="B3" s="16">
         <v>-3.1643783178642977E-2</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="23">
         <v>-43.788649604404455</v>
       </c>
     </row>
@@ -10005,10 +10081,10 @@
       <c r="A4" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="18">
+      <c r="B4" s="16">
         <v>0.10662251610112376</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="23">
         <v>181.14425108512822</v>
       </c>
     </row>
@@ -10016,10 +10092,10 @@
       <c r="A5" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="18">
+      <c r="B5" s="16">
         <v>0.22352718656723969</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="23">
         <v>435.41748460652605</v>
       </c>
     </row>
@@ -10027,10 +10103,10 @@
       <c r="A6" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="B6" s="18">
+      <c r="B6" s="16">
         <v>0.27812413208890713</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="23">
         <v>578.64448749668736</v>
       </c>
     </row>
@@ -10038,10 +10114,10 @@
       <c r="A7" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B7" s="16">
         <v>0.36841687474264384</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="23">
         <v>877.67950550398723</v>
       </c>
     </row>
@@ -10049,10 +10125,10 @@
       <c r="A8" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="B8" s="18">
+      <c r="B8" s="16">
         <v>0.41014721340805782</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="23">
         <v>1045.3709705081908</v>
       </c>
     </row>
@@ -10060,10 +10136,10 @@
       <c r="A9" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B9" s="18">
+      <c r="B9" s="16">
         <v>0.45993380444662985</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="23">
         <v>1281.6009810282249</v>
       </c>
     </row>
@@ -10071,10 +10147,10 @@
       <c r="A10" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="B10" s="18">
+      <c r="B10" s="16">
         <v>0.51055115420046859</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="23">
         <v>1569.7545498141037</v>
       </c>
     </row>
@@ -10082,10 +10158,10 @@
       <c r="A11" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B11" s="18">
+      <c r="B11" s="16">
         <v>0.54218751207076643</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="23">
         <v>1780.1367483920326</v>
       </c>
     </row>
@@ -10093,10 +10169,10 @@
       <c r="A12" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="16">
         <v>0.57106524574927675</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="23">
         <v>2001.0074137192757</v>
       </c>
     </row>
@@ -10104,10 +10180,10 @@
       <c r="A13" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="16">
         <v>0.600741965177646</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="23">
         <v>2264.7309070085066</v>
       </c>
     </row>
@@ -10115,10 +10191,10 @@
       <c r="A14" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="16">
         <v>0.61428454469029115</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="23">
         <v>2394.9387346725953</v>
       </c>
     </row>
@@ -10126,10 +10202,10 @@
       <c r="A15" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="16">
         <v>0.6384674576092837</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="23">
         <v>2653.1498838932571</v>
       </c>
     </row>
@@ -10137,10 +10213,10 @@
       <c r="A16" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="16">
         <v>0.65563208379195637</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="23">
         <v>2861.4090332557985</v>
       </c>
     </row>
@@ -10148,10 +10224,10 @@
       <c r="A17" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="16">
         <v>0.67324311852121121</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="23">
         <v>3098.1163877218828</v>
       </c>
     </row>
@@ -10159,10 +10235,10 @@
       <c r="A18" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B18" s="18">
+      <c r="B18" s="16">
         <v>0.68722372020327338</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="23">
         <v>3301.2712584388055</v>
       </c>
     </row>
@@ -10170,10 +10246,10 @@
       <c r="A19" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="16">
         <v>0.70393277636813412</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="23">
         <v>3572.8449228752056</v>
       </c>
     </row>
@@ -10181,10 +10257,10 @@
       <c r="A20" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="16">
         <v>0.71714180087360224</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="23">
         <v>3807.9376423537938</v>
       </c>
     </row>
@@ -10192,21 +10268,21 @@
       <c r="A21" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="16">
         <v>0.72596116523362819</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="23">
         <v>3980.9100067437248</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B22" s="18">
+        <v>208</v>
+      </c>
+      <c r="B22" s="16">
         <v>0.43133482816833502</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="23">
         <v>1737.8685551686087</v>
       </c>
     </row>
@@ -10229,35 +10305,35 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C1" t="s">
         <v>212</v>
       </c>
-      <c r="C1" t="s">
-        <v>213</v>
-      </c>
       <c r="D1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="69">
+      <c r="B2">
         <v>667.0627481481481</v>
       </c>
-      <c r="C2" s="25">
+      <c r="C2" s="23">
         <v>3278.7910210078066</v>
       </c>
-      <c r="D2" s="25">
+      <c r="D2" s="23">
         <v>1775.604462143609</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="16">
         <v>0.42093221594715907</v>
       </c>
     </row>
@@ -10265,39 +10341,39 @@
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="69">
+      <c r="B3">
         <v>666.09559696969711</v>
       </c>
-      <c r="C3" s="25">
+      <c r="C3" s="23">
         <v>3209.7407013607803</v>
       </c>
-      <c r="D3" s="25">
+      <c r="D3" s="23">
         <v>1706.9937221890627</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="16">
         <v>0.43984605634929735</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B4" s="69">
+        <v>208</v>
+      </c>
+      <c r="B4">
         <v>666.53081499999996</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="23">
         <v>3240.813345201942</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="23">
         <v>1737.8685551686085</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="16">
         <v>0.43133482816833485</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="57" t="s">
-        <v>198</v>
+      <c r="A6" s="51" t="s">
+        <v>197</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15">
@@ -10306,8 +10382,8 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="57" t="s">
-        <v>199</v>
+      <c r="A7" s="51" t="s">
+        <v>198</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15">
@@ -10316,11 +10392,11 @@
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="57" t="s">
-        <v>200</v>
+      <c r="A8" s="51" t="s">
+        <v>199</v>
       </c>
       <c r="B8" s="15"/>
-      <c r="C8" s="58">
+      <c r="C8" s="52">
         <f>C6*10*4*365</f>
         <v>1008134.6668465839</v>
       </c>
@@ -10350,7 +10426,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C1" t="s">
         <v>177</v>
@@ -10374,14 +10450,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1306.9186975909088</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.77841666666666</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="23">
         <f>B2*D2</f>
         <v>0</v>
       </c>
@@ -10389,12 +10465,12 @@
         <f>C2*D2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="66" t="s">
+      <c r="H2" s="81" t="s">
         <v>184</v>
       </c>
-      <c r="I2" s="67"/>
-      <c r="J2" s="67"/>
-      <c r="K2" s="68"/>
+      <c r="I2" s="82"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="83"/>
     </row>
     <row r="3" spans="1:11" ht="23" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" t="str">
@@ -10405,14 +10481,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3898.8371549557341</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>669.68241666666677</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="25">
+      <c r="E3" s="23">
         <f t="shared" ref="E3:E66" si="0">B3*D3</f>
         <v>3898.8371549557341</v>
       </c>
@@ -10420,11 +10496,11 @@
         <f t="shared" ref="F3:F66" si="1">C3*D3</f>
         <v>669.68241666666677</v>
       </c>
-      <c r="H3" s="28" t="s">
-        <v>222</v>
+      <c r="H3" s="26" t="s">
+        <v>221</v>
       </c>
       <c r="I3" s="9"/>
-      <c r="K3" s="29"/>
+      <c r="K3" s="27"/>
     </row>
     <row r="4" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="str">
@@ -10435,14 +10511,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2915.2741731513229</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.18925000000002</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10450,12 +10526,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H4" s="72" t="s">
-        <v>221</v>
-      </c>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
+      <c r="H4" s="84" t="s">
+        <v>220</v>
+      </c>
+      <c r="I4" s="84"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="84"/>
     </row>
     <row r="5" spans="1:11" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="str">
@@ -10466,14 +10542,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2313.8345366644426</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>671.3356666666665</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10481,12 +10557,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H5" s="73" t="s">
+      <c r="H5" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="I5" s="74"/>
-      <c r="J5" s="74"/>
-      <c r="K5" s="75"/>
+      <c r="I5" s="86"/>
+      <c r="J5" s="86"/>
+      <c r="K5" s="87"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="str">
@@ -10497,14 +10573,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>321.41952421318661</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>672.51433333333341</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10512,8 +10588,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H6" s="30"/>
-      <c r="K6" s="29"/>
+      <c r="H6" s="28"/>
+      <c r="K6" s="27"/>
     </row>
     <row r="7" spans="1:11" ht="22" x14ac:dyDescent="0.3">
       <c r="A7" t="str">
@@ -10524,14 +10600,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>323.26840595735621</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.2076666666668</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10539,12 +10615,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="35">
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="33">
         <f>SUM(F:F)</f>
         <v>7976.8377499999997</v>
       </c>
@@ -10558,14 +10634,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-119.14322802088009</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>672.1955833333335</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10573,8 +10649,8 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H8" s="30"/>
-      <c r="K8" s="29"/>
+      <c r="H8" s="28"/>
+      <c r="K8" s="27"/>
     </row>
     <row r="9" spans="1:11" ht="22" x14ac:dyDescent="0.3">
       <c r="A9" t="str">
@@ -10585,14 +10661,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3520.5151537649854</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>665.0626666666667</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="23">
         <f t="shared" si="0"/>
         <v>3520.5151537649854</v>
       </c>
@@ -10600,10 +10676,10 @@
         <f t="shared" si="1"/>
         <v>665.0626666666667</v>
       </c>
-      <c r="H9" s="36" t="s">
+      <c r="H9" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="K9" s="37">
+      <c r="K9" s="35">
         <f>SUM(E:E)</f>
         <v>45921.803036527788</v>
       </c>
@@ -10617,14 +10693,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2327.5146895111066</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>665.55849999999987</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10632,10 +10708,10 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H10" s="33" t="s">
+      <c r="H10" s="31" t="s">
         <v>183</v>
       </c>
-      <c r="K10" s="38">
+      <c r="K10" s="36">
         <f>COUNTIF(D2:D101, 1)/100</f>
         <v>0.12</v>
       </c>
@@ -10649,14 +10725,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2810.9704623044272</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>660.83533333333321</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10664,12 +10740,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H11" s="33" t="s">
+      <c r="H11" s="31" t="s">
         <v>186</v>
       </c>
-      <c r="I11" s="34"/>
-      <c r="J11" s="34"/>
-      <c r="K11" s="39">
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="37">
         <f>K7/8000</f>
         <v>0.99710471874999995</v>
       </c>
@@ -10683,14 +10759,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-285.46823622444435</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>666.86891666666656</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10698,12 +10774,12 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H12" s="40" t="s">
+      <c r="H12" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="I12" s="27"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="41">
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="39">
         <f>K9/K7</f>
         <v>5.7568932045192707</v>
       </c>
@@ -10717,14 +10793,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3987.6477913956414</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.33449999999993</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="23">
         <f t="shared" si="0"/>
         <v>3987.6477913956414</v>
       </c>
@@ -10742,14 +10818,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3370.6209363796747</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>660.86791666666659</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10767,14 +10843,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>578.64448749668736</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.19141666666656</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10792,14 +10868,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>439.4590568763972</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.30966666666654</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10817,14 +10893,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>445.64430600711876</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.33974999999998</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10842,14 +10918,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>992.32641442903105</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.93216666666672</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10867,14 +10943,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1985.083259011737</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>662.95749999999998</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10892,14 +10968,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1564.2131000006318</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.03941666666674</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10917,14 +10993,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>930.0238820023003</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>672.1686666666667</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10942,14 +11018,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2375.1230218062628</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.12533333333329</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10967,14 +11043,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>248.77526682307735</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.73608333333323</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -10992,14 +11068,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>938.19566229737052</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.25358333333327</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11017,14 +11093,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1270.1460764882788</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.71325000000002</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11042,14 +11118,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1676.7643367544392</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>661.26316666666673</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11067,14 +11143,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3153.6525396018942</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.25900000000013</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11092,14 +11168,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>521.66725026817448</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.15458333333322</v>
       </c>
       <c r="D28">
         <v>0</v>
       </c>
-      <c r="E28" s="25">
+      <c r="E28" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11117,14 +11193,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1937.4522661945857</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.57799999999986</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11142,14 +11218,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2286.1979421014134</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.32133333333331</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11167,14 +11243,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-170.30271887112167</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>669.57758333333334</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11192,14 +11268,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2357.5757757786951</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.07933333333335</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11217,14 +11293,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>390.99730825947859</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.04674999999997</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11242,14 +11318,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-84.827357121797604</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>665.68316666666658</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11267,14 +11343,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3893.0589787511108</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.28916666666657</v>
       </c>
       <c r="D35">
         <v>1</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="23">
         <f t="shared" si="0"/>
         <v>3893.0589787511108</v>
       </c>
@@ -11292,14 +11368,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3968.4536238355167</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.21125000000006</v>
       </c>
       <c r="D36">
         <v>1</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="23">
         <f t="shared" si="0"/>
         <v>3968.4536238355167</v>
       </c>
@@ -11317,14 +11393,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3261.2916015240753</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.3442500000001</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11342,14 +11418,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>992.78970294683495</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>666.59124999999995</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
-      <c r="E38" s="25">
+      <c r="E38" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11367,14 +11443,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>60.596079695393883</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.69500000000005</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
-      <c r="E39" s="25">
+      <c r="E39" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11392,14 +11468,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2700.5219726380396</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.81100000000004</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
-      <c r="E40" s="25">
+      <c r="E40" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11417,14 +11493,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1600.723059050428</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.97158333333334</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E41" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11442,14 +11518,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>171.51916735706004</v>
       </c>
-      <c r="C42" s="24">
+      <c r="C42" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>665.88858333333337</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11467,14 +11543,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1852.2716010562717</v>
       </c>
-      <c r="C43" s="24">
+      <c r="C43" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>662.30583333333334</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
-      <c r="E43" s="25">
+      <c r="E43" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11492,14 +11568,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-224.87677609262846</v>
       </c>
-      <c r="C44" s="24">
+      <c r="C44" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.22783333333336</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
-      <c r="E44" s="25">
+      <c r="E44" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11517,14 +11593,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3714.7087354656305</v>
       </c>
-      <c r="C45" s="24">
+      <c r="C45" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.96491666666668</v>
       </c>
       <c r="D45">
         <v>1</v>
       </c>
-      <c r="E45" s="25">
+      <c r="E45" s="23">
         <f t="shared" si="0"/>
         <v>3714.7087354656305</v>
       </c>
@@ -11542,14 +11618,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>787.61939220007594</v>
       </c>
-      <c r="C46" s="24">
+      <c r="C46" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.21124999999995</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
-      <c r="E46" s="25">
+      <c r="E46" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11567,14 +11643,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2605.7777951484745</v>
       </c>
-      <c r="C47" s="24">
+      <c r="C47" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>661.31133333333332</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
-      <c r="E47" s="25">
+      <c r="E47" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11592,14 +11668,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1024.6889507356827</v>
       </c>
-      <c r="C48" s="24">
+      <c r="C48" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>666.67624999999998</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
-      <c r="E48" s="25">
+      <c r="E48" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11617,14 +11693,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1964.0079480779264</v>
       </c>
-      <c r="C49" s="24">
+      <c r="C49" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>662.90791666666678</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
-      <c r="E49" s="25">
+      <c r="E49" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11642,14 +11718,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2079.8686531558697</v>
       </c>
-      <c r="C50" s="24">
+      <c r="C50" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>671.77341666666655</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
-      <c r="E50" s="25">
+      <c r="E50" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11667,14 +11743,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>453.56758819820493</v>
       </c>
-      <c r="C51" s="24">
+      <c r="C51" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.2627500000001</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
-      <c r="E51" s="25">
+      <c r="E51" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11692,14 +11768,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3988.1024266071795</v>
       </c>
-      <c r="C52" s="24">
+      <c r="C52" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>660.11424999999997</v>
       </c>
       <c r="D52">
         <v>1</v>
       </c>
-      <c r="E52" s="25">
+      <c r="E52" s="23">
         <f t="shared" si="0"/>
         <v>3988.1024266071795</v>
       </c>
@@ -11717,14 +11793,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3108.0984845694602</v>
       </c>
-      <c r="C53" s="24">
+      <c r="C53" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>671.05091666666658</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11742,14 +11818,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3851.2584303721842</v>
       </c>
-      <c r="C54" s="24">
+      <c r="C54" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.32299999999998</v>
       </c>
       <c r="D54">
         <v>1</v>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="23">
         <f t="shared" si="0"/>
         <v>3851.2584303721842</v>
       </c>
@@ -11767,14 +11843,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3650.8292919244195</v>
       </c>
-      <c r="C55" s="24">
+      <c r="C55" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>662.01825000000008</v>
       </c>
       <c r="D55">
         <v>1</v>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="23">
         <f t="shared" si="0"/>
         <v>3650.8292919244195</v>
       </c>
@@ -11792,14 +11868,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2312.3033496498833</v>
       </c>
-      <c r="C56" s="24">
+      <c r="C56" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.19475000000011</v>
       </c>
       <c r="D56">
         <v>0</v>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11817,14 +11893,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3772.7244248262482</v>
       </c>
-      <c r="C57" s="24">
+      <c r="C57" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>661.61308333333318</v>
       </c>
       <c r="D57">
         <v>1</v>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="23">
         <f t="shared" si="0"/>
         <v>3772.7244248262482</v>
       </c>
@@ -11842,14 +11918,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>17.620153678082033</v>
       </c>
-      <c r="C58" s="24">
+      <c r="C58" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>672.36416666666662</v>
       </c>
       <c r="D58">
         <v>0</v>
       </c>
-      <c r="E58" s="25">
+      <c r="E58" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11867,14 +11943,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>504.41100310837555</v>
       </c>
-      <c r="C59" s="24">
+      <c r="C59" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>665.57833333333326</v>
       </c>
       <c r="D59">
         <v>0</v>
       </c>
-      <c r="E59" s="25">
+      <c r="E59" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11892,14 +11968,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-174.78749990257893</v>
       </c>
-      <c r="C60" s="24">
+      <c r="C60" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.33499999999992</v>
       </c>
       <c r="D60">
         <v>0</v>
       </c>
-      <c r="E60" s="25">
+      <c r="E60" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11917,14 +11993,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1086.3754517680231</v>
       </c>
-      <c r="C61" s="24">
+      <c r="C61" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>665.79649999999992</v>
       </c>
       <c r="D61">
         <v>0</v>
       </c>
-      <c r="E61" s="25">
+      <c r="E61" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11942,14 +12018,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1370.7478058248912</v>
       </c>
-      <c r="C62" s="24">
+      <c r="C62" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.3123333333333</v>
       </c>
       <c r="D62">
         <v>0</v>
       </c>
-      <c r="E62" s="25">
+      <c r="E62" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11967,14 +12043,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>843.74678076030955</v>
       </c>
-      <c r="C63" s="24">
+      <c r="C63" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>665.16466666666679</v>
       </c>
       <c r="D63">
         <v>0</v>
       </c>
-      <c r="E63" s="25">
+      <c r="E63" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -11992,14 +12068,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3351.13083007257</v>
       </c>
-      <c r="C64" s="24">
+      <c r="C64" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.06583333333333</v>
       </c>
       <c r="D64">
         <v>0</v>
       </c>
-      <c r="E64" s="25">
+      <c r="E64" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -12017,14 +12093,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1225.6714851211523</v>
       </c>
-      <c r="C65" s="24">
+      <c r="C65" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.43324999999993</v>
       </c>
       <c r="D65">
         <v>0</v>
       </c>
-      <c r="E65" s="25">
+      <c r="E65" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -12042,14 +12118,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>888.81181025988008</v>
       </c>
-      <c r="C66" s="24">
+      <c r="C66" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>660.91750000000002</v>
       </c>
       <c r="D66">
         <v>0</v>
       </c>
-      <c r="E66" s="25">
+      <c r="E66" s="23">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -12067,14 +12143,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2065.7015858787845</v>
       </c>
-      <c r="C67" s="24">
+      <c r="C67" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.19974999999999</v>
       </c>
       <c r="D67">
         <v>0</v>
       </c>
-      <c r="E67" s="25">
+      <c r="E67" s="23">
         <f t="shared" ref="E67:E101" si="2">B67*D67</f>
         <v>0</v>
       </c>
@@ -12092,14 +12168,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>256.30522960865414</v>
       </c>
-      <c r="C68" s="24">
+      <c r="C68" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>666.33058333333327</v>
       </c>
       <c r="D68">
         <v>0</v>
       </c>
-      <c r="E68" s="25">
+      <c r="E68" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12117,14 +12193,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3230.9264295042885</v>
       </c>
-      <c r="C69" s="24">
+      <c r="C69" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.76441666666665</v>
       </c>
       <c r="D69">
         <v>0</v>
       </c>
-      <c r="E69" s="25">
+      <c r="E69" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12142,14 +12218,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-42.789906774364454</v>
       </c>
-      <c r="C70" s="24">
+      <c r="C70" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.24149999999997</v>
       </c>
       <c r="D70">
         <v>0</v>
       </c>
-      <c r="E70" s="25">
+      <c r="E70" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12167,14 +12243,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>4061.5090369245499</v>
       </c>
-      <c r="C71" s="24">
+      <c r="C71" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>669.91333333333341</v>
       </c>
       <c r="D71">
         <v>1</v>
       </c>
-      <c r="E71" s="25">
+      <c r="E71" s="23">
         <f t="shared" si="2"/>
         <v>4061.5090369245499</v>
       </c>
@@ -12192,14 +12268,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3096.990123501625</v>
       </c>
-      <c r="C72" s="24">
+      <c r="C72" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>666.8972500000001</v>
       </c>
       <c r="D72">
         <v>0</v>
       </c>
-      <c r="E72" s="25">
+      <c r="E72" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12217,14 +12293,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>518.32291857044243</v>
       </c>
-      <c r="C73" s="24">
+      <c r="C73" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>662.02674999999999</v>
       </c>
       <c r="D73">
         <v>0</v>
       </c>
-      <c r="E73" s="25">
+      <c r="E73" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12242,14 +12318,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-354.06731627712247</v>
       </c>
-      <c r="C74" s="24">
+      <c r="C74" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.66949999999997</v>
       </c>
       <c r="D74">
         <v>0</v>
       </c>
-      <c r="E74" s="25">
+      <c r="E74" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12267,14 +12343,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3292.3864947134198</v>
       </c>
-      <c r="C75" s="24">
+      <c r="C75" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.87</v>
       </c>
       <c r="D75">
         <v>0</v>
       </c>
-      <c r="E75" s="25">
+      <c r="E75" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12292,14 +12368,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2803.1323984253886</v>
       </c>
-      <c r="C76" s="24">
+      <c r="C76" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>666.04866666666669</v>
       </c>
       <c r="D76">
         <v>0</v>
       </c>
-      <c r="E76" s="25">
+      <c r="E76" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12317,14 +12393,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2904.368681739998</v>
       </c>
-      <c r="C77" s="24">
+      <c r="C77" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>662.61183333333327</v>
       </c>
       <c r="D77">
         <v>0</v>
       </c>
-      <c r="E77" s="25">
+      <c r="E77" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12342,14 +12418,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3091.7874828645326</v>
       </c>
-      <c r="C78" s="24">
+      <c r="C78" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.69641666666666</v>
       </c>
       <c r="D78">
         <v>0</v>
       </c>
-      <c r="E78" s="25">
+      <c r="E78" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12367,14 +12443,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-45.786094418815765</v>
       </c>
-      <c r="C79" s="24">
+      <c r="C79" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>668.82391666666672</v>
       </c>
       <c r="D79">
         <v>0</v>
       </c>
-      <c r="E79" s="25">
+      <c r="E79" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12392,14 +12468,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1234.5208401158932</v>
       </c>
-      <c r="C80" s="24">
+      <c r="C80" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.91725000000008</v>
       </c>
       <c r="D80">
         <v>0</v>
       </c>
-      <c r="E80" s="25">
+      <c r="E80" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12417,14 +12493,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>142.30333341863911</v>
       </c>
-      <c r="C81" s="24">
+      <c r="C81" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>669.08883333333335</v>
       </c>
       <c r="D81">
         <v>0</v>
       </c>
-      <c r="E81" s="25">
+      <c r="E81" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12442,14 +12518,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3505.8772581068374</v>
       </c>
-      <c r="C82" s="24">
+      <c r="C82" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>666.84625000000005</v>
       </c>
       <c r="D82">
         <v>0</v>
       </c>
-      <c r="E82" s="25">
+      <c r="E82" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12467,14 +12543,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2424.5571073906772</v>
       </c>
-      <c r="C83" s="24">
+      <c r="C83" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>671.67849999999999</v>
       </c>
       <c r="D83">
         <v>0</v>
       </c>
-      <c r="E83" s="25">
+      <c r="E83" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12492,14 +12568,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1112.7197846146994</v>
       </c>
-      <c r="C84" s="24">
+      <c r="C84" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>662.95891666666671</v>
       </c>
       <c r="D84">
         <v>0</v>
       </c>
-      <c r="E84" s="25">
+      <c r="E84" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12517,14 +12593,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-92.190194268449204</v>
       </c>
-      <c r="C85" s="24">
+      <c r="C85" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.09841666666659</v>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
-      <c r="E85" s="25">
+      <c r="E85" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12542,14 +12618,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1023.0031810538137</v>
       </c>
-      <c r="C86" s="24">
+      <c r="C86" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.17</v>
       </c>
       <c r="D86">
         <v>0</v>
       </c>
-      <c r="E86" s="25">
+      <c r="E86" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12567,14 +12643,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1085.6933080092508</v>
       </c>
-      <c r="C87" s="24">
+      <c r="C87" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>665.84183333333328</v>
       </c>
       <c r="D87">
         <v>0</v>
       </c>
-      <c r="E87" s="25">
+      <c r="E87" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12592,14 +12668,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2903.5962425212883</v>
       </c>
-      <c r="C88" s="24">
+      <c r="C88" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.24200000000008</v>
       </c>
       <c r="D88">
         <v>0</v>
       </c>
-      <c r="E88" s="25">
+      <c r="E88" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12617,14 +12693,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2489.923078876237</v>
       </c>
-      <c r="C89" s="24">
+      <c r="C89" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>669.04066666666665</v>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
-      <c r="E89" s="25">
+      <c r="E89" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12642,14 +12718,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3614.1579877045806</v>
       </c>
-      <c r="C90" s="24">
+      <c r="C90" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.31091666666669</v>
       </c>
       <c r="D90">
         <v>1</v>
       </c>
-      <c r="E90" s="25">
+      <c r="E90" s="23">
         <f t="shared" si="2"/>
         <v>3614.1579877045806</v>
       </c>
@@ -12667,14 +12743,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1749.4796721176608</v>
       </c>
-      <c r="C91" s="24">
+      <c r="C91" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>661.12433333333331</v>
       </c>
       <c r="D91">
         <v>0</v>
       </c>
-      <c r="E91" s="25">
+      <c r="E91" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12692,14 +12768,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>160.98417338902436</v>
       </c>
-      <c r="C92" s="24">
+      <c r="C92" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>664.87</v>
       </c>
       <c r="D92">
         <v>0</v>
       </c>
-      <c r="E92" s="25">
+      <c r="E92" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12717,14 +12793,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2831.1122413923663</v>
       </c>
-      <c r="C93" s="24">
+      <c r="C93" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.72883333333334</v>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
-      <c r="E93" s="25">
+      <c r="E93" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12742,14 +12818,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3047.9241765538163</v>
       </c>
-      <c r="C94" s="24">
+      <c r="C94" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>661.39066666666668</v>
       </c>
       <c r="D94">
         <v>0</v>
       </c>
-      <c r="E94" s="25">
+      <c r="E94" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12767,14 +12843,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>2146.5877996182885</v>
       </c>
-      <c r="C95" s="24">
+      <c r="C95" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>669.20358333333343</v>
       </c>
       <c r="D95">
         <v>0</v>
       </c>
-      <c r="E95" s="25">
+      <c r="E95" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12792,14 +12868,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>3090.2455192399684</v>
       </c>
-      <c r="C96" s="24">
+      <c r="C96" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>669.08741666666651</v>
       </c>
       <c r="D96">
         <v>0</v>
       </c>
-      <c r="E96" s="25">
+      <c r="E96" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12817,14 +12893,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1842.0313836397581</v>
       </c>
-      <c r="C97" s="24">
+      <c r="C97" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>671.16000000000008</v>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
-      <c r="E97" s="25">
+      <c r="E97" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12842,14 +12918,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1973.9307699967503</v>
       </c>
-      <c r="C98" s="24">
+      <c r="C98" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.45966666666664</v>
       </c>
       <c r="D98">
         <v>0</v>
       </c>
-      <c r="E98" s="25">
+      <c r="E98" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12867,14 +12943,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>1544.3274903912516</v>
       </c>
-      <c r="C99" s="24">
+      <c r="C99" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>670.18816666666658</v>
       </c>
       <c r="D99">
         <v>0</v>
       </c>
-      <c r="E99" s="25">
+      <c r="E99" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12892,14 +12968,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>-262.34927742934951</v>
       </c>
-      <c r="C100" s="24">
+      <c r="C100" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>663.86983333333342</v>
       </c>
       <c r="D100">
         <v>0</v>
       </c>
-      <c r="E100" s="25">
+      <c r="E100" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -12917,14 +12993,14 @@
         <f>Alice_Master_Analysis[[#This Row],[Net Profit]]</f>
         <v>106.97833591431436</v>
       </c>
-      <c r="C101" s="24">
+      <c r="C101" s="22">
         <f>Alice_Master_Analysis[[#This Row],[Net_kWh_used]]</f>
         <v>667.82516666666663</v>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
-      <c r="E101" s="25">
+      <c r="E101" s="23">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -13009,27 +13085,27 @@
       <c r="H1" s="3"/>
     </row>
     <row r="2" spans="2:8" ht="23" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="81"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="57"/>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="2:8" ht="23" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="40" t="s">
-        <v>223</v>
-      </c>
-      <c r="C3" s="83" t="s">
+      <c r="B3" s="38" t="s">
+        <v>222</v>
+      </c>
+      <c r="C3" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D3" s="84">
+      <c r="D3" s="60">
         <v>2200</v>
       </c>
-      <c r="E3" s="85" t="s">
+      <c r="E3" s="61" t="s">
         <v>109</v>
       </c>
       <c r="F3" s="3"/>
@@ -13037,14 +13113,14 @@
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B4" s="51"/>
-      <c r="C4" s="94" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="70" t="s">
         <v>151</v>
       </c>
-      <c r="D4" s="84">
+      <c r="D4" s="60">
         <v>35</v>
       </c>
-      <c r="E4" s="85" t="s">
+      <c r="E4" s="61" t="s">
         <v>152</v>
       </c>
       <c r="F4" s="3"/>
@@ -13052,14 +13128,14 @@
       <c r="H4" s="3"/>
     </row>
     <row r="5" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B5" s="51"/>
-      <c r="C5" s="83" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="59" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="84">
+      <c r="D5" s="60">
         <v>58</v>
       </c>
-      <c r="E5" s="85" t="s">
+      <c r="E5" s="61" t="s">
         <v>154</v>
       </c>
       <c r="F5" s="3"/>
@@ -13067,14 +13143,14 @@
       <c r="H5" s="3"/>
     </row>
     <row r="6" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B6" s="51"/>
-      <c r="C6" s="83" t="s">
+      <c r="B6" s="45"/>
+      <c r="C6" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="D6" s="84">
+      <c r="D6" s="60">
         <v>2.25</v>
       </c>
-      <c r="E6" s="85" t="s">
+      <c r="E6" s="61" t="s">
         <v>123</v>
       </c>
       <c r="F6" s="3"/>
@@ -13082,114 +13158,114 @@
       <c r="H6" s="3"/>
     </row>
     <row r="7" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B7" s="51"/>
+      <c r="B7" s="45"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="54"/>
-      <c r="E7" s="55"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="49"/>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
     <row r="8" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B8" s="51"/>
+      <c r="B8" s="45"/>
       <c r="C8" s="8"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="53"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="47"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
     <row r="9" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B9" s="82" t="s">
+      <c r="B9" s="58" t="s">
         <v>166</v>
       </c>
-      <c r="C9" s="86" t="s">
+      <c r="C9" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="D9" s="87">
+      <c r="D9" s="63">
         <v>1.17432263</v>
       </c>
-      <c r="E9" s="88"/>
+      <c r="E9" s="64"/>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
     <row r="10" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B10" s="78"/>
-      <c r="C10" s="93" t="s">
-        <v>225</v>
-      </c>
-      <c r="D10" s="87">
+      <c r="B10" s="54"/>
+      <c r="C10" s="69" t="s">
+        <v>224</v>
+      </c>
+      <c r="D10" s="63">
         <v>1.0008E-4</v>
       </c>
-      <c r="E10" s="88"/>
+      <c r="E10" s="64"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
     <row r="11" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B11" s="78"/>
-      <c r="C11" s="86" t="s">
-        <v>226</v>
-      </c>
-      <c r="D11" s="87">
+      <c r="B11" s="54"/>
+      <c r="C11" s="62" t="s">
+        <v>225</v>
+      </c>
+      <c r="D11" s="63">
         <f>-0.01089176</f>
         <v>-1.089176E-2</v>
       </c>
-      <c r="E11" s="88"/>
+      <c r="E11" s="64"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
     <row r="12" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B12" s="78"/>
-      <c r="C12" s="86" t="s">
-        <v>224</v>
-      </c>
-      <c r="D12" s="87">
+      <c r="B12" s="54"/>
+      <c r="C12" s="62" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="63">
         <v>1.81E-8</v>
       </c>
-      <c r="E12" s="88"/>
+      <c r="E12" s="64"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
     <row r="13" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B13" s="78"/>
-      <c r="C13" s="86" t="s">
-        <v>227</v>
-      </c>
-      <c r="D13" s="87">
+      <c r="B13" s="54"/>
+      <c r="C13" s="62" t="s">
+        <v>226</v>
+      </c>
+      <c r="D13" s="63">
         <v>-9.0699999999999996E-7</v>
       </c>
-      <c r="E13" s="88"/>
+      <c r="E13" s="64"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
     <row r="14" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B14" s="78"/>
-      <c r="C14" s="86" t="s">
-        <v>228</v>
-      </c>
-      <c r="D14" s="87">
+      <c r="B14" s="54"/>
+      <c r="C14" s="62" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="63">
         <v>2.5076999999999999E-4</v>
       </c>
-      <c r="E14" s="88"/>
+      <c r="E14" s="64"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
     <row r="15" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B15" s="78"/>
-      <c r="C15" s="86" t="s">
+      <c r="B15" s="54"/>
+      <c r="C15" s="62" t="s">
         <v>156</v>
       </c>
-      <c r="D15" s="89">
+      <c r="D15" s="65">
         <f>D9 + (D10*D3) + (D11*D4) + (D12*(D3^2)) + (D13*D3*D4) + (D14*(D4^2))</f>
         <v>1.3382452799999998</v>
       </c>
-      <c r="E15" s="85" t="s">
+      <c r="E15" s="61" t="s">
         <v>157</v>
       </c>
       <c r="F15" s="3"/>
@@ -13197,139 +13273,139 @@
       <c r="H15" s="3"/>
     </row>
     <row r="16" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B16" s="78"/>
+      <c r="B16" s="54"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="79"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="55"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
     <row r="17" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B17" s="82" t="s">
+      <c r="B17" s="58" t="s">
         <v>165</v>
       </c>
-      <c r="C17" s="90" t="s">
+      <c r="C17" s="66" t="s">
         <v>158</v>
       </c>
-      <c r="D17" s="91">
+      <c r="D17" s="67">
         <f>100-D5*D15</f>
         <v>22.381773760000016</v>
       </c>
-      <c r="E17" s="85" t="s">
-        <v>229</v>
+      <c r="E17" s="61" t="s">
+        <v>228</v>
       </c>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
     <row r="18" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B18" s="78"/>
-      <c r="C18" s="95" t="s">
+      <c r="B18" s="54"/>
+      <c r="C18" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="92" t="str">
+      <c r="D18" s="68" t="str">
         <f>IF(C17 &lt; 20, "REJECTED", "CLEARED")</f>
         <v>CLEARED</v>
       </c>
-      <c r="E18" s="85" t="s">
+      <c r="E18" s="61" t="s">
         <v>169</v>
       </c>
       <c r="F18" s="3"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="19"/>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="2:8" ht="20" x14ac:dyDescent="0.2">
-      <c r="B19" s="78"/>
+      <c r="B19" s="54"/>
       <c r="C19" s="8"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="53"/>
+      <c r="D19" s="50"/>
+      <c r="E19" s="47"/>
       <c r="F19" s="3"/>
       <c r="G19" s="1"/>
-      <c r="H19" s="20"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B20" s="97" t="s">
+      <c r="B20" s="73" t="s">
         <v>164</v>
       </c>
-      <c r="C20" s="90" t="s">
+      <c r="C20" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="96">
+      <c r="D20" s="72">
         <f>D3*D6</f>
         <v>4950</v>
       </c>
-      <c r="E20" s="88"/>
+      <c r="E20" s="64"/>
       <c r="F20" s="3"/>
       <c r="G20" s="1"/>
-      <c r="H20" s="21"/>
+      <c r="H20" s="19"/>
     </row>
     <row r="21" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B21" s="51"/>
-      <c r="C21" s="90" t="s">
+      <c r="B21" s="45"/>
+      <c r="C21" s="66" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="96">
+      <c r="D21" s="72">
         <f>( (100 - D17) / 100 * val_capacity ) * val_elec_rate * val_charging_loss</f>
         <v>133.00659248486397</v>
       </c>
-      <c r="E21" s="98"/>
+      <c r="E21" s="74"/>
       <c r="F21" s="8"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="21"/>
+      <c r="H21" s="19"/>
     </row>
     <row r="22" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B22" s="51"/>
-      <c r="C22" s="90" t="s">
+      <c r="B22" s="45"/>
+      <c r="C22" s="66" t="s">
         <v>168</v>
       </c>
-      <c r="D22" s="96">
+      <c r="D22" s="72">
         <f>(val_battery_cost / val_cycle) * ( 1 + (D3 / val_max_payload) * val_stress_factor )</f>
         <v>284.66666666666669</v>
       </c>
-      <c r="E22" s="98"/>
+      <c r="E22" s="74"/>
       <c r="F22" s="8"/>
       <c r="G22" s="1"/>
-      <c r="H22" s="21"/>
+      <c r="H22" s="19"/>
     </row>
     <row r="23" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B23" s="51"/>
-      <c r="C23" s="90" t="s">
+      <c r="B23" s="45"/>
+      <c r="C23" s="66" t="s">
         <v>160</v>
       </c>
-      <c r="D23" s="96">
+      <c r="D23" s="72">
         <f>D22+D21+val_ground_ops</f>
         <v>1617.6732591515306</v>
       </c>
-      <c r="E23" s="88"/>
+      <c r="E23" s="64"/>
       <c r="F23" s="9"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="20"/>
+      <c r="H23" s="18"/>
     </row>
     <row r="24" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B24" s="32"/>
-      <c r="C24" s="90" t="s">
+      <c r="B24" s="30"/>
+      <c r="C24" s="66" t="s">
         <v>161</v>
       </c>
-      <c r="D24" s="96">
+      <c r="D24" s="72">
         <f>D20-D23</f>
         <v>3332.3267408484694</v>
       </c>
-      <c r="E24" s="88"/>
+      <c r="E24" s="64"/>
       <c r="F24" s="9"/>
       <c r="G24" s="1"/>
-      <c r="H24" s="22"/>
+      <c r="H24" s="20"/>
     </row>
     <row r="25" spans="2:8" ht="22" x14ac:dyDescent="0.3">
-      <c r="B25" s="52"/>
-      <c r="C25" s="90" t="s">
+      <c r="B25" s="46"/>
+      <c r="C25" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="D25" s="99">
+      <c r="D25" s="75">
         <f>D24/D20</f>
         <v>0.67319732138352917</v>
       </c>
-      <c r="E25" s="88"/>
+      <c r="E25" s="64"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
